--- a/data/재난현장지도_표준화_데이터.xlsx
+++ b/data/재난현장지도_표준화_데이터.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\★ 경영평가총괄TF팀\12. AX\재해지도 만들기_규식\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\kdr\2.TextDocument\구호사업팀(재해구호관리팀)\--- 2026 구호사업팀\1. 이사랑_2026년 업무\6. 대처현황 상황보고\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -2827,16 +2827,16 @@
         <v>336</v>
       </c>
       <c r="C14" s="29">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="D14" s="29">
-        <v>5000000</v>
+        <v>35840</v>
       </c>
       <c r="E14" s="29">
         <v>10742</v>
       </c>
       <c r="F14" s="29">
-        <v>1200</v>
+        <v>1230</v>
       </c>
       <c r="G14" s="29">
         <v>625</v>
@@ -2844,7 +2844,7 @@
       <c r="H14" s="29"/>
       <c r="I14" s="30">
         <f>SUM(B14:H14)</f>
-        <v>5013003</v>
+        <v>49173</v>
       </c>
     </row>
     <row r="15" spans="1:9">

--- a/data/재난현장지도_표준화_데이터.xlsx
+++ b/data/재난현장지도_표준화_데이터.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\kdr\2.TextDocument\구호사업팀(재해구호관리팀)\--- 2026 구호사업팀\1. 이사랑_2026년 업무\6. 대처현황 상황보고\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사랑\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31366908-D8A6-45DC-8CE2-192D359A20B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="18000" windowHeight="24765" activeTab="3"/>
+    <workbookView xWindow="14535" yWindow="2775" windowWidth="14100" windowHeight="12585" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="00_사용안내" sheetId="1" r:id="rId1"/>
@@ -21,12 +22,28 @@
     <sheet name="대설" sheetId="7" r:id="rId7"/>
     <sheet name="지진" sheetId="8" r:id="rId8"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="545" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="131">
   <si>
     <t>재난 및 구호 현장지도 데이터 표준안</t>
   </si>
@@ -526,11 +543,15 @@
   <si>
     <t>누적 강수량</t>
   </si>
+  <si>
+    <t>kg</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
     <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="177" formatCode="0.0"/>
@@ -1164,7 +1185,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Normal" xfId="1"/>
+    <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1374,7 +1395,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
@@ -1484,7 +1505,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:I9"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
@@ -1736,7 +1757,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:K40"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
@@ -2578,7 +2599,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:I40"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
@@ -2833,18 +2854,20 @@
         <v>35840</v>
       </c>
       <c r="E14" s="29">
-        <v>10742</v>
+        <v>13012</v>
       </c>
       <c r="F14" s="29">
-        <v>1230</v>
+        <v>2344</v>
       </c>
       <c r="G14" s="29">
         <v>625</v>
       </c>
-      <c r="H14" s="29"/>
+      <c r="H14" s="29">
+        <v>1800</v>
+      </c>
       <c r="I14" s="30">
         <f>SUM(B14:H14)</f>
-        <v>49173</v>
+        <v>54357</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -2869,7 +2892,9 @@
       <c r="G15" s="32" t="s">
         <v>79</v>
       </c>
-      <c r="H15" s="32"/>
+      <c r="H15" s="32" t="s">
+        <v>130</v>
+      </c>
       <c r="I15" s="33"/>
     </row>
     <row r="16" spans="1:9">
@@ -3247,7 +3272,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:J40"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
@@ -3862,7 +3887,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:J40"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
@@ -4477,7 +4502,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:J40"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
@@ -5092,7 +5117,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:J40"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>

--- a/data/재난현장지도_표준화_데이터.xlsx
+++ b/data/재난현장지도_표준화_데이터.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사랑\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31366908-D8A6-45DC-8CE2-192D359A20B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDE5320C-6A16-4BCD-B915-58970EE237F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14535" yWindow="2775" windowWidth="14100" windowHeight="12585" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12405" yWindow="765" windowWidth="16395" windowHeight="12585" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="00_사용안내" sheetId="1" r:id="rId1"/>
@@ -2863,11 +2863,11 @@
         <v>625</v>
       </c>
       <c r="H14" s="29">
-        <v>1800</v>
+        <v>3140</v>
       </c>
       <c r="I14" s="30">
         <f>SUM(B14:H14)</f>
-        <v>54357</v>
+        <v>55697</v>
       </c>
     </row>
     <row r="15" spans="1:9">

--- a/data/재난현장지도_표준화_데이터.xlsx
+++ b/data/재난현장지도_표준화_데이터.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사랑\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDE5320C-6A16-4BCD-B915-58970EE237F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53321090-2242-4782-BDDA-BE059AD74DB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12405" yWindow="765" windowWidth="16395" windowHeight="12585" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11475" yWindow="0" windowWidth="16395" windowHeight="17385" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="00_사용안내" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="132">
   <si>
     <t>재난 및 구호 현장지도 데이터 표준안</t>
   </si>
@@ -547,6 +547,10 @@
     <t>kg</t>
     <phoneticPr fontId="13" type="noConversion"/>
   </si>
+  <si>
+    <t>식품·간식</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -557,7 +561,7 @@
     <numFmt numFmtId="177" formatCode="0.0"/>
     <numFmt numFmtId="178" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -667,6 +671,14 @@
       <color rgb="FF111827"/>
       <name val="돋움"/>
       <family val="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF111827"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
   </fonts>
   <fills count="7">
@@ -949,7 +961,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1182,6 +1194,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2824,8 +2839,8 @@
       <c r="D13" s="26" t="s">
         <v>69</v>
       </c>
-      <c r="E13" s="26" t="s">
-        <v>70</v>
+      <c r="E13" s="83" t="s">
+        <v>131</v>
       </c>
       <c r="F13" s="66" t="s">
         <v>71</v>
@@ -2854,7 +2869,7 @@
         <v>35840</v>
       </c>
       <c r="E14" s="29">
-        <v>13012</v>
+        <v>16056</v>
       </c>
       <c r="F14" s="29">
         <v>2344</v>
@@ -2863,11 +2878,11 @@
         <v>625</v>
       </c>
       <c r="H14" s="29">
-        <v>3140</v>
+        <v>9660</v>
       </c>
       <c r="I14" s="30">
         <f>SUM(B14:H14)</f>
-        <v>55697</v>
+        <v>65261</v>
       </c>
     </row>
     <row r="15" spans="1:9">

--- a/data/재난현장지도_표준화_데이터.xlsx
+++ b/data/재난현장지도_표준화_데이터.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사랑\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\kdr\2.TextDocument\구호사업팀(재해구호관리팀)\--- 2026 구호사업팀\1. 이사랑_2026년 업무\6. 대처현황 상황보고\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53321090-2242-4782-BDDA-BE059AD74DB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11475" yWindow="0" windowWidth="16395" windowHeight="17385" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15990" windowHeight="8280" firstSheet="1" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="00_사용안내" sheetId="1" r:id="rId1"/>
@@ -22,28 +21,12 @@
     <sheet name="대설" sheetId="7" r:id="rId7"/>
     <sheet name="지진" sheetId="8" r:id="rId8"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="131">
   <si>
     <t>재난 및 구호 현장지도 데이터 표준안</t>
   </si>
@@ -54,13 +37,360 @@
     <t>작성·운영 원칙</t>
   </si>
   <si>
+    <t>재해별 시트</t>
+  </si>
+  <si>
+    <t>폭염·호우 등 재해마다 피해지표가 다르므로 시트를 구분합니다.</t>
+  </si>
+  <si>
+    <t>공통 메타데이터</t>
+  </si>
+  <si>
+    <t>재해구분, 자료구분, 시작일, 종료일, 기준일, 지도단위, 기본 원형지표, 지표단위를 동일 위치에 둡니다.</t>
+  </si>
+  <si>
+    <t>구호현황</t>
+  </si>
+  <si>
+    <t>모든 시트에서 동일한 7개 품목 구조를 사용하며, 합계는 수식으로 계산합니다.</t>
+  </si>
+  <si>
+    <t>피해현황</t>
+  </si>
+  <si>
+    <t>위치정보(시도·시군구·지점명·위도·경도)를 앞쪽에 두고 이후 재해별 피해지표를 배치합니다.</t>
+  </si>
+  <si>
+    <t>전국/부분지역</t>
+  </si>
+  <si>
+    <t>전국 자료는 모든 지역을 입력하고, 특정 지역 피해만 있으면 해당 행만 입력합니다. 빈 지역행을 만들 필요는 없습니다.</t>
+  </si>
+  <si>
+    <t>지점자료</t>
+  </si>
+  <si>
+    <t>가덕도·성산처럼 시군구보다 세부 지점인 경우 '지점명'에 입력하고 시군구는 확인 가능한 경우만 입력합니다.</t>
+  </si>
+  <si>
+    <t>웹·지도 연계 설정</t>
+  </si>
+  <si>
+    <t>재해구분</t>
+  </si>
+  <si>
+    <t>시트명</t>
+  </si>
+  <si>
+    <t>자료구분</t>
+  </si>
+  <si>
+    <t>지도단위</t>
+  </si>
+  <si>
+    <t>기본 원형지표</t>
+  </si>
+  <si>
+    <t>단위</t>
+  </si>
+  <si>
+    <t>보조지표1</t>
+  </si>
+  <si>
+    <t>보조지표2</t>
+  </si>
+  <si>
+    <t>비고</t>
+  </si>
+  <si>
+    <t>폭염</t>
+  </si>
+  <si>
+    <t>실데이터</t>
+  </si>
+  <si>
+    <t>시도</t>
+  </si>
+  <si>
+    <t>온열질환자</t>
+  </si>
+  <si>
+    <t>명</t>
+  </si>
+  <si>
+    <t>사망자</t>
+  </si>
+  <si>
+    <t>가축피해</t>
+  </si>
+  <si>
+    <t>전남광주는 원자료상 결합표기이므로 지도 연계 시 확인 필요</t>
+  </si>
+  <si>
+    <t>호우</t>
+  </si>
+  <si>
+    <t>시군구/지점</t>
+  </si>
+  <si>
+    <t>강수량</t>
+  </si>
+  <si>
+    <t>mm</t>
+  </si>
+  <si>
+    <t>부상자</t>
+  </si>
+  <si>
+    <t>가덕도·성산은 관측 지점명으로 관리</t>
+  </si>
+  <si>
+    <t>태풍</t>
+  </si>
+  <si>
+    <t>가상데이터</t>
+  </si>
+  <si>
+    <t>시군구</t>
+  </si>
+  <si>
+    <t>최대순간풍속</t>
+  </si>
+  <si>
+    <t>m/s</t>
+  </si>
+  <si>
+    <t>대피인원</t>
+  </si>
+  <si>
+    <t>예시</t>
+  </si>
+  <si>
+    <t>산불</t>
+  </si>
+  <si>
+    <t>산불피해면적</t>
+  </si>
+  <si>
+    <t>ha</t>
+  </si>
+  <si>
+    <t>주택피해</t>
+  </si>
+  <si>
+    <t>대설</t>
+  </si>
+  <si>
+    <t>최심적설</t>
+  </si>
+  <si>
+    <t>cm</t>
+  </si>
+  <si>
+    <t>시설피해</t>
+  </si>
+  <si>
+    <t>고립인원</t>
+  </si>
+  <si>
+    <t>지진</t>
+  </si>
+  <si>
+    <t>진도</t>
+  </si>
+  <si>
+    <t>MMI</t>
+  </si>
+  <si>
+    <t>재난 및 구호 현장지도 데이터 - 폭염</t>
+  </si>
+  <si>
+    <t>시작일</t>
+  </si>
+  <si>
+    <t>종료일</t>
+  </si>
+  <si>
+    <t>기준일</t>
+  </si>
+  <si>
+    <t>지표단위</t>
+  </si>
+  <si>
+    <t>생수</t>
+  </si>
+  <si>
+    <t>간식</t>
+  </si>
+  <si>
+    <t>쉘터 및 바닥매트</t>
+  </si>
+  <si>
+    <t>합계</t>
+  </si>
+  <si>
+    <t>수량</t>
+  </si>
+  <si>
+    <t>시도/권역</t>
+  </si>
+  <si>
+    <t>지점명</t>
+  </si>
+  <si>
+    <t>위도</t>
+  </si>
+  <si>
+    <t>경도</t>
+  </si>
+  <si>
+    <t>양식피해</t>
+  </si>
+  <si>
+    <t>폭염주의보</t>
+  </si>
+  <si>
+    <t>열대야주의보</t>
+  </si>
+  <si>
+    <t>서울</t>
+  </si>
+  <si>
+    <t>전남광주</t>
+  </si>
+  <si>
+    <t>부산</t>
+  </si>
+  <si>
+    <t>대구</t>
+  </si>
+  <si>
+    <t>인천</t>
+  </si>
+  <si>
+    <t>대전</t>
+  </si>
+  <si>
+    <t>울산</t>
+  </si>
+  <si>
+    <t>세종</t>
+  </si>
+  <si>
+    <t>경기</t>
+  </si>
+  <si>
+    <t>강원</t>
+  </si>
+  <si>
+    <t>충북</t>
+  </si>
+  <si>
+    <t>충남</t>
+  </si>
+  <si>
+    <t>전북</t>
+  </si>
+  <si>
+    <t>경북</t>
+  </si>
+  <si>
+    <t>경남</t>
+  </si>
+  <si>
+    <t>제주</t>
+  </si>
+  <si>
+    <t>※ '전남광주'는 제공받은 원자료의 결합 표기를 그대로 유지했습니다. 지도에 개별 시도 버블을 표시하려면 향후 광주광역시와 전라남도 값을 분리한 원자료가 필요합니다.</t>
+  </si>
+  <si>
+    <t>재난 및 구호 현장지도 데이터 - 호우</t>
+  </si>
+  <si>
+    <t>개</t>
+  </si>
+  <si>
+    <t>동</t>
+  </si>
+  <si>
+    <t>병</t>
+  </si>
+  <si>
+    <t>세트</t>
+  </si>
+  <si>
+    <t>강수량(mm)</t>
+  </si>
+  <si>
+    <t>거제</t>
+  </si>
+  <si>
+    <t>통영</t>
+  </si>
+  <si>
+    <t>가덕도</t>
+  </si>
+  <si>
+    <t>관측 지점</t>
+  </si>
+  <si>
+    <t>성산</t>
+  </si>
+  <si>
+    <t>사천</t>
+  </si>
+  <si>
+    <t>고성</t>
+  </si>
+  <si>
+    <t>강수량 값 미제공</t>
+  </si>
+  <si>
+    <t>재난 및 구호 현장지도 데이터 - 태풍</t>
+  </si>
+  <si>
+    <t>※ 가상데이터 예시
+웹·지도 연계 구조 테스트용이며 실제 피해통계가 아닙니다.</t>
+  </si>
+  <si>
+    <t>최대순간풍속(m/s)</t>
+  </si>
+  <si>
+    <t>주택피해(동)</t>
+  </si>
+  <si>
+    <t>정전가구</t>
+  </si>
+  <si>
+    <t>재난 및 구호 현장지도 데이터 - 산불</t>
+  </si>
+  <si>
+    <t>산불피해면적(ha)</t>
+  </si>
+  <si>
+    <t>재난 및 구호 현장지도 데이터 - 대설</t>
+  </si>
+  <si>
+    <t>최심적설(cm)</t>
+  </si>
+  <si>
+    <t>시설피해(건)</t>
+  </si>
+  <si>
+    <t>교통통제(개소)</t>
+  </si>
+  <si>
+    <t>재난 및 구호 현장지도 데이터 - 지진</t>
+  </si>
+  <si>
+    <t>진도(MMI)</t>
+  </si>
+  <si>
+    <t>여진횟수</t>
+  </si>
+  <si>
     <t>검토사항</t>
-  </si>
-  <si>
-    <t>재해별 시트</t>
-  </si>
-  <si>
-    <t>폭염·호우 등 재해마다 피해지표가 다르므로 시트를 구분합니다.</t>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -68,6 +398,7 @@
         <sz val="11"/>
         <rFont val="돋움"/>
         <family val="3"/>
+        <charset val="129"/>
       </rPr>
       <t>재해</t>
     </r>
@@ -83,6 +414,7 @@
         <sz val="11"/>
         <rFont val="돋움"/>
         <family val="3"/>
+        <charset val="129"/>
       </rPr>
       <t>추가여부</t>
     </r>
@@ -98,226 +430,23 @@
         <sz val="11"/>
         <rFont val="돋움"/>
         <family val="3"/>
+        <charset val="129"/>
       </rPr>
       <t>검토</t>
     </r>
-  </si>
-  <si>
-    <t>공통 메타데이터</t>
-  </si>
-  <si>
-    <t>재해구분, 자료구분, 시작일, 종료일, 기준일, 지도단위, 기본 원형지표, 지표단위를 동일 위치에 둡니다.</t>
-  </si>
-  <si>
-    <t>구호현황</t>
-  </si>
-  <si>
-    <t>모든 시트에서 동일한 7개 품목 구조를 사용하며, 합계는 수식으로 계산합니다.</t>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>구호품목 표준화 검토</t>
-  </si>
-  <si>
-    <t>피해현황</t>
-  </si>
-  <si>
-    <t>위치정보(시도·시군구·지점명·위도·경도)를 앞쪽에 두고 이후 재해별 피해지표를 배치합니다.</t>
-  </si>
-  <si>
-    <t>전국/부분지역</t>
-  </si>
-  <si>
-    <t>전국 자료는 모든 지역을 입력하고, 특정 지역 피해만 있으면 해당 행만 입력합니다. 빈 지역행을 만들 필요는 없습니다.</t>
-  </si>
-  <si>
-    <t>지점자료</t>
-  </si>
-  <si>
-    <t>가덕도·성산처럼 시군구보다 세부 지점인 경우 '지점명'에 입력하고 시군구는 확인 가능한 경우만 입력합니다.</t>
-  </si>
-  <si>
-    <t>웹·지도 연계 설정</t>
-  </si>
-  <si>
-    <t>재해구분</t>
-  </si>
-  <si>
-    <t>시트명</t>
-  </si>
-  <si>
-    <t>자료구분</t>
-  </si>
-  <si>
-    <t>지도단위</t>
-  </si>
-  <si>
-    <t>기본 원형지표</t>
-  </si>
-  <si>
-    <t>단위</t>
-  </si>
-  <si>
-    <t>보조지표1</t>
-  </si>
-  <si>
-    <t>보조지표2</t>
-  </si>
-  <si>
-    <t>비고</t>
-  </si>
-  <si>
-    <t>폭염</t>
-  </si>
-  <si>
-    <t>실데이터</t>
-  </si>
-  <si>
-    <t>시도</t>
-  </si>
-  <si>
-    <t>온열질환자</t>
-  </si>
-  <si>
-    <t>명</t>
-  </si>
-  <si>
-    <t>사망자</t>
-  </si>
-  <si>
-    <t>가축피해</t>
-  </si>
-  <si>
-    <t>전남광주는 원자료상 결합표기이므로 지도 연계 시 확인 필요</t>
-  </si>
-  <si>
-    <t>호우</t>
-  </si>
-  <si>
-    <t>시군구/지점</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-      </rPr>
-      <t>누적</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-      </rPr>
-      <t>강수량</t>
-    </r>
-  </si>
-  <si>
-    <t>mm</t>
-  </si>
-  <si>
-    <t>부상자</t>
-  </si>
-  <si>
-    <t>가덕도·성산은 관측 지점명으로 관리</t>
-  </si>
-  <si>
-    <t>태풍</t>
-  </si>
-  <si>
-    <t>가상데이터</t>
-  </si>
-  <si>
-    <t>시군구</t>
-  </si>
-  <si>
-    <t>최대순간풍속</t>
-  </si>
-  <si>
-    <t>m/s</t>
-  </si>
-  <si>
-    <t>강수량</t>
-  </si>
-  <si>
-    <t>대피인원</t>
-  </si>
-  <si>
-    <t>예시</t>
-  </si>
-  <si>
-    <t>산불</t>
-  </si>
-  <si>
-    <t>산불피해면적</t>
-  </si>
-  <si>
-    <t>ha</t>
-  </si>
-  <si>
-    <t>주택피해</t>
-  </si>
-  <si>
-    <t>대설</t>
-  </si>
-  <si>
-    <t>최심적설</t>
-  </si>
-  <si>
-    <t>cm</t>
-  </si>
-  <si>
-    <t>시설피해</t>
-  </si>
-  <si>
-    <t>고립인원</t>
-  </si>
-  <si>
-    <t>지진</t>
-  </si>
-  <si>
-    <t>진도</t>
-  </si>
-  <si>
-    <t>MMI</t>
-  </si>
-  <si>
-    <t>재난 및 구호 현장지도 데이터 - 폭염</t>
-  </si>
-  <si>
-    <t>시작일</t>
-  </si>
-  <si>
-    <t>종료일</t>
-  </si>
-  <si>
-    <t>기준일</t>
-  </si>
-  <si>
-    <t>지표단위</t>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>구호키트</t>
-  </si>
-  <si>
-    <t>쉘터 및 바닥매트</t>
-  </si>
-  <si>
-    <t>생수</t>
-  </si>
-  <si>
-    <t>간식</t>
-  </si>
-  <si>
-    <t>자원봉사자키트</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>세탁차량</t>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -330,105 +459,15 @@
         <color rgb="FF111827"/>
         <rFont val="돋움"/>
         <family val="3"/>
+        <charset val="129"/>
       </rPr>
       <t>출동키트</t>
     </r>
-  </si>
-  <si>
-    <t>세탁차량</t>
-  </si>
-  <si>
-    <t>합계</t>
-  </si>
-  <si>
-    <t>수량</t>
-  </si>
-  <si>
-    <t>개</t>
-  </si>
-  <si>
-    <t>동</t>
-  </si>
-  <si>
-    <t>병</t>
-  </si>
-  <si>
-    <t>세트</t>
-  </si>
-  <si>
-    <t>시도/권역</t>
-  </si>
-  <si>
-    <t>지점명</t>
-  </si>
-  <si>
-    <t>위도</t>
-  </si>
-  <si>
-    <t>경도</t>
-  </si>
-  <si>
-    <t>양식피해</t>
-  </si>
-  <si>
-    <t>폭염주의보</t>
-  </si>
-  <si>
-    <t>열대야주의보</t>
-  </si>
-  <si>
-    <t>서울</t>
-  </si>
-  <si>
-    <t>전남광주</t>
-  </si>
-  <si>
-    <t>부산</t>
-  </si>
-  <si>
-    <t>대구</t>
-  </si>
-  <si>
-    <t>인천</t>
-  </si>
-  <si>
-    <t>대전</t>
-  </si>
-  <si>
-    <t>울산</t>
-  </si>
-  <si>
-    <t>세종</t>
-  </si>
-  <si>
-    <t>경기</t>
-  </si>
-  <si>
-    <t>강원</t>
-  </si>
-  <si>
-    <t>충북</t>
-  </si>
-  <si>
-    <t>충남</t>
-  </si>
-  <si>
-    <t>전북</t>
-  </si>
-  <si>
-    <t>경북</t>
-  </si>
-  <si>
-    <t>경남</t>
-  </si>
-  <si>
-    <t>제주</t>
-  </si>
-  <si>
-    <t>※ '전남광주'는 제공받은 원자료의 결합 표기를 그대로 유지했습니다. 지도에 개별 시도 버블을 표시하려면 향후 광주광역시와 전라남도 값을 분리한 원자료가 필요합니다.</t>
-  </si>
-  <si>
-    <t>재난 및 구호 현장지도 데이터 - 호우</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>자원봉사자키트</t>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -438,6 +477,7 @@
         <color rgb="FF111827"/>
         <rFont val="돋움"/>
         <family val="3"/>
+        <charset val="129"/>
       </rPr>
       <t>누적</t>
     </r>
@@ -457,6 +497,7 @@
         <color rgb="FF111827"/>
         <rFont val="돋움"/>
         <family val="3"/>
+        <charset val="129"/>
       </rPr>
       <t>강수량</t>
     </r>
@@ -469,99 +510,55 @@
       </rPr>
       <t>(mm)</t>
     </r>
-  </si>
-  <si>
-    <t>거제</t>
-  </si>
-  <si>
-    <t>통영</t>
-  </si>
-  <si>
-    <t>가덕도</t>
-  </si>
-  <si>
-    <t>관측 지점</t>
-  </si>
-  <si>
-    <t>성산</t>
-  </si>
-  <si>
-    <t>사천</t>
-  </si>
-  <si>
-    <t>고성</t>
-  </si>
-  <si>
-    <t>강수량 값 미제공</t>
-  </si>
-  <si>
-    <t>재난 및 구호 현장지도 데이터 - 태풍</t>
-  </si>
-  <si>
-    <t>※ 가상데이터 예시
-웹·지도 연계 구조 테스트용이며 실제 피해통계가 아닙니다.</t>
-  </si>
-  <si>
-    <t>최대순간풍속(m/s)</t>
-  </si>
-  <si>
-    <t>강수량(mm)</t>
-  </si>
-  <si>
-    <t>주택피해(동)</t>
-  </si>
-  <si>
-    <t>정전가구</t>
-  </si>
-  <si>
-    <t>재난 및 구호 현장지도 데이터 - 산불</t>
-  </si>
-  <si>
-    <t>산불피해면적(ha)</t>
-  </si>
-  <si>
-    <t>재난 및 구호 현장지도 데이터 - 대설</t>
-  </si>
-  <si>
-    <t>최심적설(cm)</t>
-  </si>
-  <si>
-    <t>시설피해(건)</t>
-  </si>
-  <si>
-    <t>교통통제(개소)</t>
-  </si>
-  <si>
-    <t>재난 및 구호 현장지도 데이터 - 지진</t>
-  </si>
-  <si>
-    <t>진도(MMI)</t>
-  </si>
-  <si>
-    <t>여진횟수</t>
-  </si>
-  <si>
-    <t>누적 강수량</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>누적</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>강수량</t>
+    </r>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>식품·간식</t>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>kg</t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
-    <t>식품·간식</t>
     <phoneticPr fontId="13" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="3">
     <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="177" formatCode="0.0"/>
     <numFmt numFmtId="178" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -657,26 +654,6 @@
       <sz val="10"/>
       <color rgb="FF111827"/>
       <name val="돋움"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="돋움"/>
-      <family val="3"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF111827"/>
-      <name val="돋움"/>
-      <family val="3"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF111827"/>
-      <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
     </font>
@@ -961,7 +938,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1149,7 +1126,6 @@
     <xf numFmtId="0" fontId="16" fillId="3" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1195,12 +1171,9 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
+    <cellStyle name="Normal" xfId="1"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1410,7 +1383,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
@@ -1420,28 +1393,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="27.95" customHeight="1">
-      <c r="A1" s="68" t="s">
+      <c r="A1" s="67" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="68" t="s">
+      <c r="B1" s="67" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="68" t="s">
+      <c r="C1" s="67" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="68" t="s">
+      <c r="D1" s="67" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="68" t="s">
+      <c r="E1" s="67" t="s">
         <v>0</v>
       </c>
-      <c r="F1" s="68" t="s">
+      <c r="F1" s="67" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="68" t="s">
+      <c r="G1" s="67" t="s">
         <v>0</v>
       </c>
-      <c r="H1" s="68" t="s">
+      <c r="H1" s="67" t="s">
         <v>0</v>
       </c>
     </row>
@@ -1453,61 +1426,61 @@
         <v>2</v>
       </c>
       <c r="C3" s="65" t="s">
-        <v>3</v>
+        <v>120</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="15">
       <c r="A4" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="6" t="s">
-        <v>5</v>
-      </c>
       <c r="C4" t="s">
-        <v>6</v>
+        <v>121</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="28.5">
       <c r="A5" s="10" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15">
       <c r="A6" s="10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C6" s="64" t="s">
-        <v>11</v>
+        <v>122</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="15">
       <c r="A7" s="10" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="28.5">
       <c r="A8" s="10" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="28.5">
       <c r="A9" s="10" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -1520,7 +1493,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I9"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
@@ -1531,235 +1504,235 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="27.95" customHeight="1">
-      <c r="A1" s="68" t="s">
-        <v>18</v>
-      </c>
-      <c r="B1" s="68" t="s">
-        <v>18</v>
-      </c>
-      <c r="C1" s="68" t="s">
-        <v>18</v>
-      </c>
-      <c r="D1" s="68" t="s">
-        <v>18</v>
-      </c>
-      <c r="E1" s="68" t="s">
-        <v>18</v>
-      </c>
-      <c r="F1" s="68" t="s">
-        <v>18</v>
-      </c>
-      <c r="G1" s="68" t="s">
-        <v>18</v>
-      </c>
-      <c r="H1" s="68" t="s">
-        <v>18</v>
-      </c>
-      <c r="I1" s="68" t="s">
-        <v>18</v>
+      <c r="A1" s="67" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="67" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="67" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="67" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" s="67" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1" s="67" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1" s="67" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1" s="67" t="s">
+        <v>15</v>
+      </c>
+      <c r="I1" s="67" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="15">
       <c r="A3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="E3" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="F3" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="G3" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="E3" s="11" t="s">
+      <c r="H3" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="F3" s="11" t="s">
+      <c r="I3" s="2" t="s">
         <v>24</v>
-      </c>
-      <c r="G3" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="H3" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="28.5">
       <c r="A4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="B4" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="C4" s="12" t="s">
+      <c r="F4" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="G4" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="H4" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="I4" s="6" t="s">
         <v>32</v>
-      </c>
-      <c r="G4" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="H4" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="E5" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="F5" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="B5" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="C5" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="D5" s="13" t="s">
+      <c r="G5" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="H5" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="E5" s="13" t="s">
+      <c r="I5" s="7" t="s">
         <v>38</v>
-      </c>
-      <c r="F5" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="G5" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="H5" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="I5" s="7" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="E6" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="C6" s="13" t="s">
+      <c r="F6" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="D6" s="13" t="s">
+      <c r="G6" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="H6" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="E6" s="13" t="s">
+      <c r="I6" s="7" t="s">
         <v>45</v>
-      </c>
-      <c r="F6" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="G6" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="H6" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="I6" s="7" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="4" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D7" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="F7" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="G7" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="E7" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="F7" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="G7" s="13" t="s">
-        <v>48</v>
-      </c>
       <c r="H7" s="13" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="E8" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="F8" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="G8" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="H8" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="B8" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="C8" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="D8" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="E8" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="F8" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="G8" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="H8" s="13" t="s">
-        <v>58</v>
-      </c>
       <c r="I8" s="7" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="5" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F9" s="14" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="G9" s="14" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="H9" s="14" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -1772,7 +1745,10 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:K40"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
@@ -1785,32 +1761,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="27.95" customHeight="1">
-      <c r="A1" s="69" t="s">
-        <v>62</v>
-      </c>
-      <c r="B1" s="69" t="s">
-        <v>62</v>
-      </c>
-      <c r="C1" s="69" t="s">
-        <v>62</v>
-      </c>
-      <c r="D1" s="69" t="s">
-        <v>62</v>
-      </c>
-      <c r="E1" s="69" t="s">
-        <v>62</v>
-      </c>
-      <c r="F1" s="69" t="s">
-        <v>62</v>
-      </c>
-      <c r="G1" s="69" t="s">
-        <v>62</v>
-      </c>
-      <c r="H1" s="69" t="s">
-        <v>62</v>
-      </c>
-      <c r="I1" s="69" t="s">
-        <v>62</v>
+      <c r="A1" s="68" t="s">
+        <v>58</v>
+      </c>
+      <c r="B1" s="68" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1" s="68" t="s">
+        <v>58</v>
+      </c>
+      <c r="D1" s="68" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1" s="68" t="s">
+        <v>58</v>
+      </c>
+      <c r="F1" s="68" t="s">
+        <v>58</v>
+      </c>
+      <c r="G1" s="68" t="s">
+        <v>58</v>
+      </c>
+      <c r="H1" s="68" t="s">
+        <v>58</v>
+      </c>
+      <c r="I1" s="68" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -1826,10 +1802,10 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="18" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C3" s="17"/>
       <c r="D3" s="17"/>
@@ -1841,10 +1817,10 @@
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="20" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C4" s="17"/>
       <c r="D4" s="17"/>
@@ -1856,7 +1832,7 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="20" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B5" s="22">
         <v>46230</v>
@@ -1871,7 +1847,7 @@
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="20" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B6" s="22"/>
       <c r="C6" s="17"/>
@@ -1884,10 +1860,10 @@
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="B7" s="67">
-        <v>46254</v>
+        <v>61</v>
+      </c>
+      <c r="B7" s="22">
+        <v>46253</v>
       </c>
       <c r="C7" s="17"/>
       <c r="D7" s="17"/>
@@ -1899,10 +1875,10 @@
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="20" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B8" s="21" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C8" s="17"/>
       <c r="D8" s="17"/>
@@ -1914,10 +1890,10 @@
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="20" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B9" s="21" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C9" s="17"/>
       <c r="D9" s="17"/>
@@ -1929,10 +1905,10 @@
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="23" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B10" s="24" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C10" s="17"/>
       <c r="D10" s="17"/>
@@ -1954,32 +1930,32 @@
       <c r="I11" s="17"/>
     </row>
     <row r="12" spans="1:9" ht="21.95" customHeight="1">
-      <c r="A12" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="B12" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="D12" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="E12" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="G12" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="H12" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="I12" s="69" t="s">
-        <v>9</v>
+      <c r="A12" s="68" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12" s="68" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="68" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" s="68" t="s">
+        <v>7</v>
+      </c>
+      <c r="E12" s="68" t="s">
+        <v>7</v>
+      </c>
+      <c r="F12" s="68" t="s">
+        <v>7</v>
+      </c>
+      <c r="G12" s="68" t="s">
+        <v>7</v>
+      </c>
+      <c r="H12" s="68" t="s">
+        <v>7</v>
+      </c>
+      <c r="I12" s="68" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -1987,69 +1963,85 @@
         <v>1</v>
       </c>
       <c r="B13" s="66" t="s">
-        <v>67</v>
+        <v>123</v>
       </c>
       <c r="C13" s="26" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D13" s="26" t="s">
-        <v>69</v>
-      </c>
-      <c r="E13" s="26" t="s">
-        <v>70</v>
+        <v>63</v>
+      </c>
+      <c r="E13" s="66" t="s">
+        <v>129</v>
       </c>
       <c r="F13" s="66" t="s">
-        <v>71</v>
+        <v>126</v>
       </c>
       <c r="G13" s="66" t="s">
-        <v>72</v>
+        <v>125</v>
       </c>
       <c r="H13" s="66" t="s">
-        <v>73</v>
+        <v>124</v>
       </c>
       <c r="I13" s="27" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="28" t="s">
-        <v>75</v>
-      </c>
-      <c r="B14" s="29"/>
-      <c r="C14" s="29"/>
-      <c r="D14" s="29"/>
-      <c r="E14" s="29"/>
-      <c r="F14" s="29"/>
-      <c r="G14" s="29"/>
-      <c r="H14" s="29"/>
+        <v>67</v>
+      </c>
+      <c r="B14" s="29">
+        <v>336</v>
+      </c>
+      <c r="C14" s="29">
+        <v>400</v>
+      </c>
+      <c r="D14" s="29">
+        <v>35840</v>
+      </c>
+      <c r="E14" s="29">
+        <v>21112</v>
+      </c>
+      <c r="F14" s="29">
+        <v>2344</v>
+      </c>
+      <c r="G14" s="29">
+        <v>625</v>
+      </c>
+      <c r="H14" s="29">
+        <v>11600</v>
+      </c>
       <c r="I14" s="30">
         <f>SUM(B14:H14)</f>
-        <v>0</v>
+        <v>72257</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="31" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B15" s="32" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="C15" s="32" t="s">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="D15" s="32" t="s">
-        <v>78</v>
+        <v>95</v>
       </c>
       <c r="E15" s="32" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="F15" s="32" t="s">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="G15" s="32" t="s">
-        <v>79</v>
-      </c>
-      <c r="H15" s="32"/>
+        <v>96</v>
+      </c>
+      <c r="H15" s="32" t="s">
+        <v>130</v>
+      </c>
       <c r="I15" s="33"/>
     </row>
     <row r="16" spans="1:9">
@@ -2064,74 +2056,74 @@
       <c r="I16" s="17"/>
     </row>
     <row r="17" spans="1:11" ht="21.95" customHeight="1">
-      <c r="A17" s="70" t="s">
-        <v>12</v>
-      </c>
-      <c r="B17" s="70" t="s">
-        <v>12</v>
-      </c>
-      <c r="C17" s="70" t="s">
-        <v>12</v>
-      </c>
-      <c r="D17" s="70" t="s">
-        <v>12</v>
-      </c>
-      <c r="E17" s="70" t="s">
-        <v>12</v>
-      </c>
-      <c r="F17" s="70" t="s">
-        <v>12</v>
-      </c>
-      <c r="G17" s="70" t="s">
-        <v>12</v>
-      </c>
-      <c r="H17" s="70" t="s">
-        <v>12</v>
-      </c>
-      <c r="I17" s="70" t="s">
-        <v>12</v>
+      <c r="A17" s="69" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" s="69" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="69" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" s="69" t="s">
+        <v>9</v>
+      </c>
+      <c r="E17" s="69" t="s">
+        <v>9</v>
+      </c>
+      <c r="F17" s="69" t="s">
+        <v>9</v>
+      </c>
+      <c r="G17" s="69" t="s">
+        <v>9</v>
+      </c>
+      <c r="H17" s="69" t="s">
+        <v>9</v>
+      </c>
+      <c r="I17" s="69" t="s">
+        <v>9</v>
       </c>
       <c r="J17" s="35"/>
       <c r="K17" s="35"/>
     </row>
     <row r="18" spans="1:11" ht="15">
       <c r="A18" s="25" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="B18" s="26" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C18" s="26" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="D18" s="26" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="E18" s="26" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="F18" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="G18" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="H18" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="G18" s="26" t="s">
-        <v>33</v>
-      </c>
-      <c r="H18" s="26" t="s">
-        <v>34</v>
-      </c>
       <c r="I18" s="26" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="J18" s="11" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
     </row>
     <row r="19" spans="1:11">
       <c r="A19" s="36" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="B19" s="37"/>
       <c r="C19" s="37"/>
@@ -2152,7 +2144,7 @@
     </row>
     <row r="20" spans="1:11">
       <c r="A20" s="41" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="B20" s="42"/>
       <c r="C20" s="42"/>
@@ -2177,7 +2169,7 @@
     </row>
     <row r="21" spans="1:11">
       <c r="A21" s="41" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="B21" s="42"/>
       <c r="C21" s="42"/>
@@ -2200,7 +2192,7 @@
     </row>
     <row r="22" spans="1:11">
       <c r="A22" s="41" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="B22" s="42"/>
       <c r="C22" s="42"/>
@@ -2221,7 +2213,7 @@
     </row>
     <row r="23" spans="1:11">
       <c r="A23" s="41" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="B23" s="42"/>
       <c r="C23" s="42"/>
@@ -2244,7 +2236,7 @@
     </row>
     <row r="24" spans="1:11">
       <c r="A24" s="41" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="B24" s="42"/>
       <c r="C24" s="42"/>
@@ -2265,7 +2257,7 @@
     </row>
     <row r="25" spans="1:11">
       <c r="A25" s="41" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="B25" s="42"/>
       <c r="C25" s="42"/>
@@ -2286,7 +2278,7 @@
     </row>
     <row r="26" spans="1:11">
       <c r="A26" s="41" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="B26" s="42"/>
       <c r="C26" s="42"/>
@@ -2307,7 +2299,7 @@
     </row>
     <row r="27" spans="1:11">
       <c r="A27" s="41" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="B27" s="42"/>
       <c r="C27" s="42"/>
@@ -2330,7 +2322,7 @@
     </row>
     <row r="28" spans="1:11">
       <c r="A28" s="41" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="B28" s="42"/>
       <c r="C28" s="42"/>
@@ -2355,7 +2347,7 @@
     </row>
     <row r="29" spans="1:11">
       <c r="A29" s="41" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="B29" s="42"/>
       <c r="C29" s="42"/>
@@ -2378,7 +2370,7 @@
     </row>
     <row r="30" spans="1:11">
       <c r="A30" s="41" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="B30" s="42"/>
       <c r="C30" s="42"/>
@@ -2403,7 +2395,7 @@
     </row>
     <row r="31" spans="1:11">
       <c r="A31" s="41" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="B31" s="42"/>
       <c r="C31" s="42"/>
@@ -2428,7 +2420,7 @@
     </row>
     <row r="32" spans="1:11">
       <c r="A32" s="41" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="B32" s="42"/>
       <c r="C32" s="42"/>
@@ -2453,7 +2445,7 @@
     </row>
     <row r="33" spans="1:11">
       <c r="A33" s="41" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="B33" s="42"/>
       <c r="C33" s="42"/>
@@ -2480,7 +2472,7 @@
     </row>
     <row r="34" spans="1:11">
       <c r="A34" s="46" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="B34" s="47"/>
       <c r="C34" s="47"/>
@@ -2520,7 +2512,7 @@
     </row>
     <row r="36" spans="1:11" ht="15">
       <c r="A36" s="25" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="B36" s="26"/>
       <c r="C36" s="26"/>
@@ -2563,32 +2555,32 @@
       <c r="I37" s="17"/>
     </row>
     <row r="38" spans="1:11">
-      <c r="A38" s="71" t="s">
-        <v>103</v>
-      </c>
-      <c r="B38" s="71"/>
-      <c r="C38" s="71"/>
-      <c r="D38" s="71"/>
-      <c r="E38" s="71"/>
-      <c r="F38" s="71"/>
-      <c r="G38" s="71"/>
-      <c r="H38" s="71"/>
-      <c r="I38" s="71"/>
-      <c r="J38" s="72"/>
-      <c r="K38" s="72"/>
+      <c r="A38" s="70" t="s">
+        <v>91</v>
+      </c>
+      <c r="B38" s="70"/>
+      <c r="C38" s="70"/>
+      <c r="D38" s="70"/>
+      <c r="E38" s="70"/>
+      <c r="F38" s="70"/>
+      <c r="G38" s="70"/>
+      <c r="H38" s="70"/>
+      <c r="I38" s="70"/>
+      <c r="J38" s="71"/>
+      <c r="K38" s="71"/>
     </row>
     <row r="39" spans="1:11">
-      <c r="A39" s="71"/>
-      <c r="B39" s="71"/>
-      <c r="C39" s="71"/>
-      <c r="D39" s="71"/>
-      <c r="E39" s="71"/>
-      <c r="F39" s="71"/>
-      <c r="G39" s="71"/>
-      <c r="H39" s="71"/>
-      <c r="I39" s="71"/>
-      <c r="J39" s="72"/>
-      <c r="K39" s="72"/>
+      <c r="A39" s="70"/>
+      <c r="B39" s="70"/>
+      <c r="C39" s="70"/>
+      <c r="D39" s="70"/>
+      <c r="E39" s="70"/>
+      <c r="F39" s="70"/>
+      <c r="G39" s="70"/>
+      <c r="H39" s="70"/>
+      <c r="I39" s="70"/>
+      <c r="J39" s="71"/>
+      <c r="K39" s="71"/>
     </row>
     <row r="40" spans="1:11">
       <c r="A40" s="17"/>
@@ -2610,11 +2602,12 @@
   </mergeCells>
   <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="69" orientation="landscape" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I40"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
@@ -2627,32 +2620,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="27.95" customHeight="1">
-      <c r="A1" s="69" t="s">
-        <v>104</v>
-      </c>
-      <c r="B1" s="69" t="s">
-        <v>104</v>
-      </c>
-      <c r="C1" s="69" t="s">
-        <v>104</v>
-      </c>
-      <c r="D1" s="69" t="s">
-        <v>104</v>
-      </c>
-      <c r="E1" s="69" t="s">
-        <v>104</v>
-      </c>
-      <c r="F1" s="69" t="s">
-        <v>104</v>
-      </c>
-      <c r="G1" s="69" t="s">
-        <v>104</v>
-      </c>
-      <c r="H1" s="69" t="s">
-        <v>104</v>
-      </c>
-      <c r="I1" s="69" t="s">
-        <v>104</v>
+      <c r="A1" s="68" t="s">
+        <v>92</v>
+      </c>
+      <c r="B1" s="68" t="s">
+        <v>92</v>
+      </c>
+      <c r="C1" s="68" t="s">
+        <v>92</v>
+      </c>
+      <c r="D1" s="68" t="s">
+        <v>92</v>
+      </c>
+      <c r="E1" s="68" t="s">
+        <v>92</v>
+      </c>
+      <c r="F1" s="68" t="s">
+        <v>92</v>
+      </c>
+      <c r="G1" s="68" t="s">
+        <v>92</v>
+      </c>
+      <c r="H1" s="68" t="s">
+        <v>92</v>
+      </c>
+      <c r="I1" s="68" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2668,10 +2661,10 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="18" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C3" s="17"/>
       <c r="D3" s="17"/>
@@ -2683,10 +2676,10 @@
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="20" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C4" s="17"/>
       <c r="D4" s="17"/>
@@ -2698,7 +2691,7 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="20" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B5" s="22">
         <v>46249</v>
@@ -2713,7 +2706,7 @@
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="20" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B6" s="22">
         <v>46253</v>
@@ -2728,10 +2721,10 @@
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="B7" s="67">
-        <v>46254</v>
+        <v>61</v>
+      </c>
+      <c r="B7" s="22">
+        <v>46253</v>
       </c>
       <c r="C7" s="17"/>
       <c r="D7" s="17"/>
@@ -2743,10 +2736,10 @@
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="20" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B8" s="21" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C8" s="17"/>
       <c r="D8" s="17"/>
@@ -2758,10 +2751,10 @@
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="20" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B9" s="21" t="s">
-        <v>129</v>
+        <v>35</v>
       </c>
       <c r="C9" s="17"/>
       <c r="D9" s="17"/>
@@ -2773,10 +2766,10 @@
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="23" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B10" s="24" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C10" s="17"/>
       <c r="D10" s="17"/>
@@ -2798,32 +2791,32 @@
       <c r="I11" s="17"/>
     </row>
     <row r="12" spans="1:9" ht="21.95" customHeight="1">
-      <c r="A12" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="B12" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="D12" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="E12" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="G12" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="H12" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="I12" s="69" t="s">
-        <v>9</v>
+      <c r="A12" s="68" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12" s="68" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="68" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" s="68" t="s">
+        <v>7</v>
+      </c>
+      <c r="E12" s="68" t="s">
+        <v>7</v>
+      </c>
+      <c r="F12" s="68" t="s">
+        <v>7</v>
+      </c>
+      <c r="G12" s="68" t="s">
+        <v>7</v>
+      </c>
+      <c r="H12" s="68" t="s">
+        <v>7</v>
+      </c>
+      <c r="I12" s="68" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -2831,85 +2824,81 @@
         <v>1</v>
       </c>
       <c r="B13" s="66" t="s">
-        <v>67</v>
+        <v>123</v>
       </c>
       <c r="C13" s="26" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D13" s="26" t="s">
-        <v>69</v>
-      </c>
-      <c r="E13" s="83" t="s">
-        <v>131</v>
+        <v>63</v>
+      </c>
+      <c r="E13" s="26" t="s">
+        <v>64</v>
       </c>
       <c r="F13" s="66" t="s">
-        <v>71</v>
+        <v>126</v>
       </c>
       <c r="G13" s="66" t="s">
-        <v>72</v>
+        <v>125</v>
       </c>
       <c r="H13" s="66" t="s">
-        <v>73</v>
+        <v>124</v>
       </c>
       <c r="I13" s="27" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="28" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="B14" s="29">
         <v>336</v>
       </c>
       <c r="C14" s="29">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="D14" s="29">
-        <v>35840</v>
+        <v>13440</v>
       </c>
       <c r="E14" s="29">
-        <v>16056</v>
+        <v>10742</v>
       </c>
       <c r="F14" s="29">
-        <v>2344</v>
+        <v>1200</v>
       </c>
       <c r="G14" s="29">
         <v>625</v>
       </c>
-      <c r="H14" s="29">
-        <v>9660</v>
-      </c>
+      <c r="H14" s="29"/>
       <c r="I14" s="30">
         <f>SUM(B14:H14)</f>
-        <v>65261</v>
+        <v>26443</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="31" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B15" s="32" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="C15" s="32" t="s">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="D15" s="32" t="s">
-        <v>78</v>
+        <v>95</v>
       </c>
       <c r="E15" s="32" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="F15" s="32" t="s">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="G15" s="32" t="s">
-        <v>79</v>
-      </c>
-      <c r="H15" s="32" t="s">
-        <v>130</v>
-      </c>
+        <v>96</v>
+      </c>
+      <c r="H15" s="32"/>
       <c r="I15" s="33"/>
     </row>
     <row r="16" spans="1:9">
@@ -2924,69 +2913,69 @@
       <c r="I16" s="17"/>
     </row>
     <row r="17" spans="1:9" ht="21.95" customHeight="1">
-      <c r="A17" s="70" t="s">
-        <v>12</v>
-      </c>
-      <c r="B17" s="70" t="s">
-        <v>12</v>
-      </c>
-      <c r="C17" s="70" t="s">
-        <v>12</v>
-      </c>
-      <c r="D17" s="70" t="s">
-        <v>12</v>
-      </c>
-      <c r="E17" s="70" t="s">
-        <v>12</v>
-      </c>
-      <c r="F17" s="70" t="s">
-        <v>12</v>
-      </c>
-      <c r="G17" s="70" t="s">
-        <v>12</v>
-      </c>
-      <c r="H17" s="70" t="s">
-        <v>12</v>
-      </c>
-      <c r="I17" s="70" t="s">
-        <v>12</v>
+      <c r="A17" s="69" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" s="69" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="69" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" s="69" t="s">
+        <v>9</v>
+      </c>
+      <c r="E17" s="69" t="s">
+        <v>9</v>
+      </c>
+      <c r="F17" s="69" t="s">
+        <v>9</v>
+      </c>
+      <c r="G17" s="69" t="s">
+        <v>9</v>
+      </c>
+      <c r="H17" s="69" t="s">
+        <v>9</v>
+      </c>
+      <c r="I17" s="69" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="B18" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="C18" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="D18" s="26" t="s">
+        <v>70</v>
+      </c>
+      <c r="E18" s="26" t="s">
+        <v>71</v>
+      </c>
+      <c r="F18" s="26" t="s">
+        <v>127</v>
+      </c>
+      <c r="G18" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="B18" s="26" t="s">
-        <v>44</v>
-      </c>
-      <c r="C18" s="26" t="s">
-        <v>81</v>
-      </c>
-      <c r="D18" s="26" t="s">
-        <v>82</v>
-      </c>
-      <c r="E18" s="26" t="s">
-        <v>83</v>
-      </c>
-      <c r="F18" s="26" t="s">
-        <v>105</v>
-      </c>
-      <c r="G18" s="26" t="s">
-        <v>33</v>
-      </c>
       <c r="H18" s="26" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="I18" s="27" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="36" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="B19" s="37" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C19" s="37"/>
       <c r="D19" s="37"/>
@@ -3004,10 +2993,10 @@
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="41" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="B20" s="42" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="C20" s="42"/>
       <c r="D20" s="42"/>
@@ -3023,11 +3012,11 @@
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="41" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="B21" s="42"/>
       <c r="C21" s="42" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="D21" s="42"/>
       <c r="E21" s="42"/>
@@ -3037,16 +3026,16 @@
       <c r="G21" s="43"/>
       <c r="H21" s="43"/>
       <c r="I21" s="55" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="41" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="B22" s="42"/>
       <c r="C22" s="42" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="D22" s="42"/>
       <c r="E22" s="42"/>
@@ -3056,15 +3045,15 @@
       <c r="G22" s="43"/>
       <c r="H22" s="43"/>
       <c r="I22" s="55" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" s="41" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="B23" s="42" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="C23" s="42"/>
       <c r="D23" s="42"/>
@@ -3078,10 +3067,10 @@
     </row>
     <row r="24" spans="1:9">
       <c r="A24" s="41" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="B24" s="42" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="C24" s="42"/>
       <c r="D24" s="42"/>
@@ -3095,7 +3084,7 @@
     </row>
     <row r="25" spans="1:9">
       <c r="A25" s="46" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="B25" s="47"/>
       <c r="C25" s="47"/>
@@ -3107,7 +3096,7 @@
         <v>1</v>
       </c>
       <c r="I25" s="57" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
     </row>
     <row r="26" spans="1:9">
@@ -3287,7 +3276,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J40"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
@@ -3300,35 +3289,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="27.95" customHeight="1">
-      <c r="A1" s="69" t="s">
-        <v>114</v>
-      </c>
-      <c r="B1" s="69" t="s">
-        <v>114</v>
-      </c>
-      <c r="C1" s="69" t="s">
-        <v>114</v>
-      </c>
-      <c r="D1" s="69" t="s">
-        <v>114</v>
-      </c>
-      <c r="E1" s="69" t="s">
-        <v>114</v>
-      </c>
-      <c r="F1" s="69" t="s">
-        <v>114</v>
-      </c>
-      <c r="G1" s="69" t="s">
-        <v>114</v>
-      </c>
-      <c r="H1" s="69" t="s">
-        <v>114</v>
-      </c>
-      <c r="I1" s="69" t="s">
-        <v>114</v>
-      </c>
-      <c r="J1" s="68" t="s">
-        <v>114</v>
+      <c r="A1" s="68" t="s">
+        <v>106</v>
+      </c>
+      <c r="B1" s="68" t="s">
+        <v>106</v>
+      </c>
+      <c r="C1" s="68" t="s">
+        <v>106</v>
+      </c>
+      <c r="D1" s="68" t="s">
+        <v>106</v>
+      </c>
+      <c r="E1" s="68" t="s">
+        <v>106</v>
+      </c>
+      <c r="F1" s="68" t="s">
+        <v>106</v>
+      </c>
+      <c r="G1" s="68" t="s">
+        <v>106</v>
+      </c>
+      <c r="H1" s="68" t="s">
+        <v>106</v>
+      </c>
+      <c r="I1" s="68" t="s">
+        <v>106</v>
+      </c>
+      <c r="J1" s="67" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -3344,52 +3333,52 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="18" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C3" s="17"/>
-      <c r="D3" s="73" t="s">
-        <v>115</v>
-      </c>
-      <c r="E3" s="74"/>
-      <c r="F3" s="74"/>
-      <c r="G3" s="74"/>
-      <c r="H3" s="74"/>
-      <c r="I3" s="75"/>
+      <c r="D3" s="72" t="s">
+        <v>107</v>
+      </c>
+      <c r="E3" s="73"/>
+      <c r="F3" s="73"/>
+      <c r="G3" s="73"/>
+      <c r="H3" s="73"/>
+      <c r="I3" s="74"/>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="20" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C4" s="17"/>
-      <c r="D4" s="76"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="78"/>
+      <c r="D4" s="75"/>
+      <c r="E4" s="76"/>
+      <c r="F4" s="76"/>
+      <c r="G4" s="76"/>
+      <c r="H4" s="76"/>
+      <c r="I4" s="77"/>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="20" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B5" s="22"/>
       <c r="C5" s="17"/>
-      <c r="D5" s="79"/>
-      <c r="E5" s="80"/>
-      <c r="F5" s="80"/>
-      <c r="G5" s="80"/>
-      <c r="H5" s="80"/>
-      <c r="I5" s="81"/>
+      <c r="D5" s="78"/>
+      <c r="E5" s="79"/>
+      <c r="F5" s="79"/>
+      <c r="G5" s="79"/>
+      <c r="H5" s="79"/>
+      <c r="I5" s="80"/>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="20" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B6" s="22"/>
       <c r="C6" s="17"/>
@@ -3402,11 +3391,9 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="B7" s="67">
-        <v>46254</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="B7" s="22"/>
       <c r="C7" s="17"/>
       <c r="D7" s="17"/>
       <c r="E7" s="17"/>
@@ -3417,10 +3404,10 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="20" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B8" s="21" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C8" s="17"/>
       <c r="D8" s="17"/>
@@ -3432,10 +3419,10 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="20" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B9" s="21" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C9" s="17"/>
       <c r="D9" s="17"/>
@@ -3447,10 +3434,10 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="23" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B10" s="24" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C10" s="17"/>
       <c r="D10" s="17"/>
@@ -3472,32 +3459,32 @@
       <c r="I11" s="17"/>
     </row>
     <row r="12" spans="1:10" ht="21.95" customHeight="1">
-      <c r="A12" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="B12" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="D12" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="E12" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="G12" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="H12" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="I12" s="69" t="s">
-        <v>9</v>
+      <c r="A12" s="68" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12" s="68" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="68" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" s="68" t="s">
+        <v>7</v>
+      </c>
+      <c r="E12" s="68" t="s">
+        <v>7</v>
+      </c>
+      <c r="F12" s="68" t="s">
+        <v>7</v>
+      </c>
+      <c r="G12" s="68" t="s">
+        <v>7</v>
+      </c>
+      <c r="H12" s="68" t="s">
+        <v>7</v>
+      </c>
+      <c r="I12" s="68" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -3505,33 +3492,33 @@
         <v>1</v>
       </c>
       <c r="B13" s="66" t="s">
-        <v>67</v>
+        <v>123</v>
       </c>
       <c r="C13" s="26" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D13" s="26" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="E13" s="26" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="F13" s="66" t="s">
-        <v>71</v>
+        <v>126</v>
       </c>
       <c r="G13" s="66" t="s">
-        <v>72</v>
+        <v>125</v>
       </c>
       <c r="H13" s="66" t="s">
-        <v>73</v>
+        <v>124</v>
       </c>
       <c r="I13" s="27" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="28" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="B14" s="29"/>
       <c r="C14" s="29"/>
@@ -3544,25 +3531,25 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="31" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B15" s="32" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="C15" s="32" t="s">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="D15" s="32" t="s">
-        <v>78</v>
+        <v>95</v>
       </c>
       <c r="E15" s="32" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="F15" s="32" t="s">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="G15" s="32" t="s">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="H15" s="32"/>
       <c r="I15" s="33"/>
@@ -3579,67 +3566,67 @@
       <c r="I16" s="17"/>
     </row>
     <row r="17" spans="1:10" ht="21.95" customHeight="1">
-      <c r="A17" s="70" t="s">
-        <v>12</v>
-      </c>
-      <c r="B17" s="70" t="s">
-        <v>12</v>
-      </c>
-      <c r="C17" s="70" t="s">
-        <v>12</v>
-      </c>
-      <c r="D17" s="70" t="s">
-        <v>12</v>
-      </c>
-      <c r="E17" s="70" t="s">
-        <v>12</v>
-      </c>
-      <c r="F17" s="70" t="s">
-        <v>12</v>
-      </c>
-      <c r="G17" s="70" t="s">
-        <v>12</v>
-      </c>
-      <c r="H17" s="70" t="s">
-        <v>12</v>
-      </c>
-      <c r="I17" s="70" t="s">
-        <v>12</v>
-      </c>
-      <c r="J17" s="82" t="s">
-        <v>12</v>
+      <c r="A17" s="69" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" s="69" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="69" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" s="69" t="s">
+        <v>9</v>
+      </c>
+      <c r="E17" s="69" t="s">
+        <v>9</v>
+      </c>
+      <c r="F17" s="69" t="s">
+        <v>9</v>
+      </c>
+      <c r="G17" s="69" t="s">
+        <v>9</v>
+      </c>
+      <c r="H17" s="69" t="s">
+        <v>9</v>
+      </c>
+      <c r="I17" s="69" t="s">
+        <v>9</v>
+      </c>
+      <c r="J17" s="81" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="15">
       <c r="A18" s="25" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B18" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="C18" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="D18" s="26" t="s">
+        <v>70</v>
+      </c>
+      <c r="E18" s="26" t="s">
+        <v>71</v>
+      </c>
+      <c r="F18" s="26" t="s">
+        <v>108</v>
+      </c>
+      <c r="G18" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="H18" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="C18" s="26" t="s">
-        <v>81</v>
-      </c>
-      <c r="D18" s="26" t="s">
-        <v>82</v>
-      </c>
-      <c r="E18" s="26" t="s">
-        <v>83</v>
-      </c>
-      <c r="F18" s="26" t="s">
-        <v>116</v>
-      </c>
-      <c r="G18" s="26" t="s">
-        <v>117</v>
-      </c>
-      <c r="H18" s="26" t="s">
-        <v>48</v>
-      </c>
       <c r="I18" s="26" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -3902,7 +3889,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J40"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
@@ -3915,35 +3902,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="27.95" customHeight="1">
-      <c r="A1" s="69" t="s">
-        <v>120</v>
-      </c>
-      <c r="B1" s="69" t="s">
-        <v>120</v>
-      </c>
-      <c r="C1" s="69" t="s">
-        <v>120</v>
-      </c>
-      <c r="D1" s="69" t="s">
-        <v>120</v>
-      </c>
-      <c r="E1" s="69" t="s">
-        <v>120</v>
-      </c>
-      <c r="F1" s="69" t="s">
-        <v>120</v>
-      </c>
-      <c r="G1" s="69" t="s">
-        <v>120</v>
-      </c>
-      <c r="H1" s="69" t="s">
-        <v>120</v>
-      </c>
-      <c r="I1" s="69" t="s">
-        <v>120</v>
-      </c>
-      <c r="J1" s="68" t="s">
-        <v>120</v>
+      <c r="A1" s="68" t="s">
+        <v>111</v>
+      </c>
+      <c r="B1" s="68" t="s">
+        <v>111</v>
+      </c>
+      <c r="C1" s="68" t="s">
+        <v>111</v>
+      </c>
+      <c r="D1" s="68" t="s">
+        <v>111</v>
+      </c>
+      <c r="E1" s="68" t="s">
+        <v>111</v>
+      </c>
+      <c r="F1" s="68" t="s">
+        <v>111</v>
+      </c>
+      <c r="G1" s="68" t="s">
+        <v>111</v>
+      </c>
+      <c r="H1" s="68" t="s">
+        <v>111</v>
+      </c>
+      <c r="I1" s="68" t="s">
+        <v>111</v>
+      </c>
+      <c r="J1" s="67" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -3959,52 +3946,52 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="18" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C3" s="17"/>
-      <c r="D3" s="73" t="s">
-        <v>115</v>
-      </c>
-      <c r="E3" s="74"/>
-      <c r="F3" s="74"/>
-      <c r="G3" s="74"/>
-      <c r="H3" s="74"/>
-      <c r="I3" s="75"/>
+      <c r="D3" s="72" t="s">
+        <v>107</v>
+      </c>
+      <c r="E3" s="73"/>
+      <c r="F3" s="73"/>
+      <c r="G3" s="73"/>
+      <c r="H3" s="73"/>
+      <c r="I3" s="74"/>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="20" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C4" s="17"/>
-      <c r="D4" s="76"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="78"/>
+      <c r="D4" s="75"/>
+      <c r="E4" s="76"/>
+      <c r="F4" s="76"/>
+      <c r="G4" s="76"/>
+      <c r="H4" s="76"/>
+      <c r="I4" s="77"/>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="20" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B5" s="22"/>
       <c r="C5" s="17"/>
-      <c r="D5" s="79"/>
-      <c r="E5" s="80"/>
-      <c r="F5" s="80"/>
-      <c r="G5" s="80"/>
-      <c r="H5" s="80"/>
-      <c r="I5" s="81"/>
+      <c r="D5" s="78"/>
+      <c r="E5" s="79"/>
+      <c r="F5" s="79"/>
+      <c r="G5" s="79"/>
+      <c r="H5" s="79"/>
+      <c r="I5" s="80"/>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="20" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B6" s="22"/>
       <c r="C6" s="17"/>
@@ -4017,11 +4004,9 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="B7" s="67">
-        <v>46254</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="B7" s="22"/>
       <c r="C7" s="17"/>
       <c r="D7" s="17"/>
       <c r="E7" s="17"/>
@@ -4032,10 +4017,10 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="20" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B8" s="21" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C8" s="17"/>
       <c r="D8" s="17"/>
@@ -4047,10 +4032,10 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="20" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B9" s="21" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="C9" s="17"/>
       <c r="D9" s="17"/>
@@ -4062,10 +4047,10 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="23" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B10" s="24" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C10" s="17"/>
       <c r="D10" s="17"/>
@@ -4087,32 +4072,32 @@
       <c r="I11" s="17"/>
     </row>
     <row r="12" spans="1:10" ht="21.95" customHeight="1">
-      <c r="A12" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="B12" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="D12" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="E12" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="G12" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="H12" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="I12" s="69" t="s">
-        <v>9</v>
+      <c r="A12" s="68" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12" s="68" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="68" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" s="68" t="s">
+        <v>7</v>
+      </c>
+      <c r="E12" s="68" t="s">
+        <v>7</v>
+      </c>
+      <c r="F12" s="68" t="s">
+        <v>7</v>
+      </c>
+      <c r="G12" s="68" t="s">
+        <v>7</v>
+      </c>
+      <c r="H12" s="68" t="s">
+        <v>7</v>
+      </c>
+      <c r="I12" s="68" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -4120,33 +4105,33 @@
         <v>1</v>
       </c>
       <c r="B13" s="66" t="s">
-        <v>67</v>
+        <v>123</v>
       </c>
       <c r="C13" s="26" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D13" s="26" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="E13" s="26" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="F13" s="66" t="s">
-        <v>71</v>
+        <v>126</v>
       </c>
       <c r="G13" s="66" t="s">
-        <v>72</v>
+        <v>125</v>
       </c>
       <c r="H13" s="66" t="s">
-        <v>73</v>
+        <v>124</v>
       </c>
       <c r="I13" s="27" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="28" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="B14" s="29"/>
       <c r="C14" s="29"/>
@@ -4159,25 +4144,25 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="31" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B15" s="32" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="C15" s="32" t="s">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="D15" s="32" t="s">
-        <v>78</v>
+        <v>95</v>
       </c>
       <c r="E15" s="32" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="F15" s="32" t="s">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="G15" s="32" t="s">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="H15" s="32"/>
       <c r="I15" s="33"/>
@@ -4194,67 +4179,67 @@
       <c r="I16" s="17"/>
     </row>
     <row r="17" spans="1:10" ht="21.95" customHeight="1">
-      <c r="A17" s="70" t="s">
-        <v>12</v>
-      </c>
-      <c r="B17" s="70" t="s">
-        <v>12</v>
-      </c>
-      <c r="C17" s="70" t="s">
-        <v>12</v>
-      </c>
-      <c r="D17" s="70" t="s">
-        <v>12</v>
-      </c>
-      <c r="E17" s="70" t="s">
-        <v>12</v>
-      </c>
-      <c r="F17" s="70" t="s">
-        <v>12</v>
-      </c>
-      <c r="G17" s="70" t="s">
-        <v>12</v>
-      </c>
-      <c r="H17" s="70" t="s">
-        <v>12</v>
-      </c>
-      <c r="I17" s="70" t="s">
-        <v>12</v>
-      </c>
-      <c r="J17" s="82" t="s">
-        <v>12</v>
+      <c r="A17" s="69" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" s="69" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="69" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" s="69" t="s">
+        <v>9</v>
+      </c>
+      <c r="E17" s="69" t="s">
+        <v>9</v>
+      </c>
+      <c r="F17" s="69" t="s">
+        <v>9</v>
+      </c>
+      <c r="G17" s="69" t="s">
+        <v>9</v>
+      </c>
+      <c r="H17" s="69" t="s">
+        <v>9</v>
+      </c>
+      <c r="I17" s="69" t="s">
+        <v>9</v>
+      </c>
+      <c r="J17" s="81" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="15">
       <c r="A18" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="B18" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="C18" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="D18" s="26" t="s">
+        <v>70</v>
+      </c>
+      <c r="E18" s="26" t="s">
+        <v>71</v>
+      </c>
+      <c r="F18" s="26" t="s">
+        <v>112</v>
+      </c>
+      <c r="G18" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="H18" s="26" t="s">
+        <v>109</v>
+      </c>
+      <c r="I18" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="B18" s="26" t="s">
-        <v>44</v>
-      </c>
-      <c r="C18" s="26" t="s">
-        <v>81</v>
-      </c>
-      <c r="D18" s="26" t="s">
-        <v>82</v>
-      </c>
-      <c r="E18" s="26" t="s">
-        <v>83</v>
-      </c>
-      <c r="F18" s="26" t="s">
-        <v>121</v>
-      </c>
-      <c r="G18" s="26" t="s">
-        <v>48</v>
-      </c>
-      <c r="H18" s="26" t="s">
-        <v>118</v>
-      </c>
-      <c r="I18" s="26" t="s">
-        <v>33</v>
-      </c>
       <c r="J18" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -4517,7 +4502,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J40"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
@@ -4530,35 +4515,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="27.95" customHeight="1">
-      <c r="A1" s="69" t="s">
-        <v>122</v>
-      </c>
-      <c r="B1" s="69" t="s">
-        <v>122</v>
-      </c>
-      <c r="C1" s="69" t="s">
-        <v>122</v>
-      </c>
-      <c r="D1" s="69" t="s">
-        <v>122</v>
-      </c>
-      <c r="E1" s="69" t="s">
-        <v>122</v>
-      </c>
-      <c r="F1" s="69" t="s">
-        <v>122</v>
-      </c>
-      <c r="G1" s="69" t="s">
-        <v>122</v>
-      </c>
-      <c r="H1" s="69" t="s">
-        <v>122</v>
-      </c>
-      <c r="I1" s="69" t="s">
-        <v>122</v>
-      </c>
-      <c r="J1" s="68" t="s">
-        <v>122</v>
+      <c r="A1" s="68" t="s">
+        <v>113</v>
+      </c>
+      <c r="B1" s="68" t="s">
+        <v>113</v>
+      </c>
+      <c r="C1" s="68" t="s">
+        <v>113</v>
+      </c>
+      <c r="D1" s="68" t="s">
+        <v>113</v>
+      </c>
+      <c r="E1" s="68" t="s">
+        <v>113</v>
+      </c>
+      <c r="F1" s="68" t="s">
+        <v>113</v>
+      </c>
+      <c r="G1" s="68" t="s">
+        <v>113</v>
+      </c>
+      <c r="H1" s="68" t="s">
+        <v>113</v>
+      </c>
+      <c r="I1" s="68" t="s">
+        <v>113</v>
+      </c>
+      <c r="J1" s="67" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -4574,52 +4559,52 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="18" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C3" s="17"/>
-      <c r="D3" s="73" t="s">
-        <v>115</v>
-      </c>
-      <c r="E3" s="74"/>
-      <c r="F3" s="74"/>
-      <c r="G3" s="74"/>
-      <c r="H3" s="74"/>
-      <c r="I3" s="75"/>
+      <c r="D3" s="72" t="s">
+        <v>107</v>
+      </c>
+      <c r="E3" s="73"/>
+      <c r="F3" s="73"/>
+      <c r="G3" s="73"/>
+      <c r="H3" s="73"/>
+      <c r="I3" s="74"/>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="20" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C4" s="17"/>
-      <c r="D4" s="76"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="78"/>
+      <c r="D4" s="75"/>
+      <c r="E4" s="76"/>
+      <c r="F4" s="76"/>
+      <c r="G4" s="76"/>
+      <c r="H4" s="76"/>
+      <c r="I4" s="77"/>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="20" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B5" s="22"/>
       <c r="C5" s="17"/>
-      <c r="D5" s="79"/>
-      <c r="E5" s="80"/>
-      <c r="F5" s="80"/>
-      <c r="G5" s="80"/>
-      <c r="H5" s="80"/>
-      <c r="I5" s="81"/>
+      <c r="D5" s="78"/>
+      <c r="E5" s="79"/>
+      <c r="F5" s="79"/>
+      <c r="G5" s="79"/>
+      <c r="H5" s="79"/>
+      <c r="I5" s="80"/>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="20" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B6" s="22"/>
       <c r="C6" s="17"/>
@@ -4632,11 +4617,9 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="B7" s="67">
-        <v>46254</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="B7" s="22"/>
       <c r="C7" s="17"/>
       <c r="D7" s="17"/>
       <c r="E7" s="17"/>
@@ -4647,10 +4630,10 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="20" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B8" s="21" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C8" s="17"/>
       <c r="D8" s="17"/>
@@ -4662,10 +4645,10 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="20" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B9" s="21" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C9" s="17"/>
       <c r="D9" s="17"/>
@@ -4677,10 +4660,10 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="23" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B10" s="24" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C10" s="17"/>
       <c r="D10" s="17"/>
@@ -4702,32 +4685,32 @@
       <c r="I11" s="17"/>
     </row>
     <row r="12" spans="1:10" ht="21.95" customHeight="1">
-      <c r="A12" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="B12" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="D12" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="E12" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="G12" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="H12" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="I12" s="69" t="s">
-        <v>9</v>
+      <c r="A12" s="68" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12" s="68" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="68" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" s="68" t="s">
+        <v>7</v>
+      </c>
+      <c r="E12" s="68" t="s">
+        <v>7</v>
+      </c>
+      <c r="F12" s="68" t="s">
+        <v>7</v>
+      </c>
+      <c r="G12" s="68" t="s">
+        <v>7</v>
+      </c>
+      <c r="H12" s="68" t="s">
+        <v>7</v>
+      </c>
+      <c r="I12" s="68" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -4735,33 +4718,33 @@
         <v>1</v>
       </c>
       <c r="B13" s="66" t="s">
-        <v>67</v>
+        <v>123</v>
       </c>
       <c r="C13" s="26" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D13" s="26" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="E13" s="26" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="F13" s="66" t="s">
-        <v>71</v>
+        <v>126</v>
       </c>
       <c r="G13" s="66" t="s">
-        <v>72</v>
+        <v>125</v>
       </c>
       <c r="H13" s="66" t="s">
-        <v>73</v>
+        <v>124</v>
       </c>
       <c r="I13" s="27" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="28" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="B14" s="29"/>
       <c r="C14" s="29"/>
@@ -4774,25 +4757,25 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="31" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B15" s="32" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="C15" s="32" t="s">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="D15" s="32" t="s">
-        <v>78</v>
+        <v>95</v>
       </c>
       <c r="E15" s="32" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="F15" s="32" t="s">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="G15" s="32" t="s">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="H15" s="32"/>
       <c r="I15" s="33"/>
@@ -4809,67 +4792,67 @@
       <c r="I16" s="17"/>
     </row>
     <row r="17" spans="1:10" ht="21.95" customHeight="1">
-      <c r="A17" s="70" t="s">
-        <v>12</v>
-      </c>
-      <c r="B17" s="70" t="s">
-        <v>12</v>
-      </c>
-      <c r="C17" s="70" t="s">
-        <v>12</v>
-      </c>
-      <c r="D17" s="70" t="s">
-        <v>12</v>
-      </c>
-      <c r="E17" s="70" t="s">
-        <v>12</v>
-      </c>
-      <c r="F17" s="70" t="s">
-        <v>12</v>
-      </c>
-      <c r="G17" s="70" t="s">
-        <v>12</v>
-      </c>
-      <c r="H17" s="70" t="s">
-        <v>12</v>
-      </c>
-      <c r="I17" s="70" t="s">
-        <v>12</v>
-      </c>
-      <c r="J17" s="82" t="s">
-        <v>12</v>
+      <c r="A17" s="69" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" s="69" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="69" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" s="69" t="s">
+        <v>9</v>
+      </c>
+      <c r="E17" s="69" t="s">
+        <v>9</v>
+      </c>
+      <c r="F17" s="69" t="s">
+        <v>9</v>
+      </c>
+      <c r="G17" s="69" t="s">
+        <v>9</v>
+      </c>
+      <c r="H17" s="69" t="s">
+        <v>9</v>
+      </c>
+      <c r="I17" s="69" t="s">
+        <v>9</v>
+      </c>
+      <c r="J17" s="81" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="15">
       <c r="A18" s="25" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B18" s="26" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C18" s="26" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="D18" s="26" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="E18" s="26" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="F18" s="26" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="G18" s="26" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="H18" s="26" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="I18" s="26" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -5132,7 +5115,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J40"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
@@ -5145,35 +5128,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="27.95" customHeight="1">
-      <c r="A1" s="69" t="s">
-        <v>126</v>
-      </c>
-      <c r="B1" s="69" t="s">
-        <v>126</v>
-      </c>
-      <c r="C1" s="69" t="s">
-        <v>126</v>
-      </c>
-      <c r="D1" s="69" t="s">
-        <v>126</v>
-      </c>
-      <c r="E1" s="69" t="s">
-        <v>126</v>
-      </c>
-      <c r="F1" s="69" t="s">
-        <v>126</v>
-      </c>
-      <c r="G1" s="69" t="s">
-        <v>126</v>
-      </c>
-      <c r="H1" s="69" t="s">
-        <v>126</v>
-      </c>
-      <c r="I1" s="69" t="s">
-        <v>126</v>
-      </c>
-      <c r="J1" s="68" t="s">
-        <v>126</v>
+      <c r="A1" s="68" t="s">
+        <v>117</v>
+      </c>
+      <c r="B1" s="68" t="s">
+        <v>117</v>
+      </c>
+      <c r="C1" s="68" t="s">
+        <v>117</v>
+      </c>
+      <c r="D1" s="68" t="s">
+        <v>117</v>
+      </c>
+      <c r="E1" s="68" t="s">
+        <v>117</v>
+      </c>
+      <c r="F1" s="68" t="s">
+        <v>117</v>
+      </c>
+      <c r="G1" s="68" t="s">
+        <v>117</v>
+      </c>
+      <c r="H1" s="68" t="s">
+        <v>117</v>
+      </c>
+      <c r="I1" s="68" t="s">
+        <v>117</v>
+      </c>
+      <c r="J1" s="67" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -5189,52 +5172,52 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="18" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C3" s="17"/>
-      <c r="D3" s="73" t="s">
-        <v>115</v>
-      </c>
-      <c r="E3" s="74"/>
-      <c r="F3" s="74"/>
-      <c r="G3" s="74"/>
-      <c r="H3" s="74"/>
-      <c r="I3" s="75"/>
+      <c r="D3" s="72" t="s">
+        <v>107</v>
+      </c>
+      <c r="E3" s="73"/>
+      <c r="F3" s="73"/>
+      <c r="G3" s="73"/>
+      <c r="H3" s="73"/>
+      <c r="I3" s="74"/>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="20" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C4" s="17"/>
-      <c r="D4" s="76"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="78"/>
+      <c r="D4" s="75"/>
+      <c r="E4" s="76"/>
+      <c r="F4" s="76"/>
+      <c r="G4" s="76"/>
+      <c r="H4" s="76"/>
+      <c r="I4" s="77"/>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="20" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B5" s="22"/>
       <c r="C5" s="17"/>
-      <c r="D5" s="79"/>
-      <c r="E5" s="80"/>
-      <c r="F5" s="80"/>
-      <c r="G5" s="80"/>
-      <c r="H5" s="80"/>
-      <c r="I5" s="81"/>
+      <c r="D5" s="78"/>
+      <c r="E5" s="79"/>
+      <c r="F5" s="79"/>
+      <c r="G5" s="79"/>
+      <c r="H5" s="79"/>
+      <c r="I5" s="80"/>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="20" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B6" s="22"/>
       <c r="C6" s="17"/>
@@ -5247,11 +5230,9 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="B7" s="67">
-        <v>46254</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="B7" s="22"/>
       <c r="C7" s="17"/>
       <c r="D7" s="17"/>
       <c r="E7" s="17"/>
@@ -5262,10 +5243,10 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="20" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B8" s="21" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C8" s="17"/>
       <c r="D8" s="17"/>
@@ -5277,10 +5258,10 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="20" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B9" s="21" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C9" s="17"/>
       <c r="D9" s="17"/>
@@ -5292,10 +5273,10 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="23" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B10" s="24" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C10" s="17"/>
       <c r="D10" s="17"/>
@@ -5317,32 +5298,32 @@
       <c r="I11" s="17"/>
     </row>
     <row r="12" spans="1:10" ht="21.95" customHeight="1">
-      <c r="A12" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="B12" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="D12" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="E12" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="G12" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="H12" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="I12" s="69" t="s">
-        <v>9</v>
+      <c r="A12" s="68" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12" s="68" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="68" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" s="68" t="s">
+        <v>7</v>
+      </c>
+      <c r="E12" s="68" t="s">
+        <v>7</v>
+      </c>
+      <c r="F12" s="68" t="s">
+        <v>7</v>
+      </c>
+      <c r="G12" s="68" t="s">
+        <v>7</v>
+      </c>
+      <c r="H12" s="68" t="s">
+        <v>7</v>
+      </c>
+      <c r="I12" s="68" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -5350,33 +5331,33 @@
         <v>1</v>
       </c>
       <c r="B13" s="66" t="s">
-        <v>67</v>
+        <v>123</v>
       </c>
       <c r="C13" s="26" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D13" s="26" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="E13" s="26" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="F13" s="66" t="s">
-        <v>71</v>
+        <v>126</v>
       </c>
       <c r="G13" s="66" t="s">
-        <v>72</v>
+        <v>125</v>
       </c>
       <c r="H13" s="66" t="s">
-        <v>73</v>
+        <v>124</v>
       </c>
       <c r="I13" s="27" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="28" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="B14" s="29"/>
       <c r="C14" s="29"/>
@@ -5389,25 +5370,25 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="31" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B15" s="32" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="C15" s="32" t="s">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="D15" s="32" t="s">
-        <v>78</v>
+        <v>95</v>
       </c>
       <c r="E15" s="32" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="F15" s="32" t="s">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="G15" s="32" t="s">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="H15" s="32"/>
       <c r="I15" s="33"/>
@@ -5424,67 +5405,67 @@
       <c r="I16" s="17"/>
     </row>
     <row r="17" spans="1:10" ht="21.95" customHeight="1">
-      <c r="A17" s="70" t="s">
-        <v>12</v>
-      </c>
-      <c r="B17" s="70" t="s">
-        <v>12</v>
-      </c>
-      <c r="C17" s="70" t="s">
-        <v>12</v>
-      </c>
-      <c r="D17" s="70" t="s">
-        <v>12</v>
-      </c>
-      <c r="E17" s="70" t="s">
-        <v>12</v>
-      </c>
-      <c r="F17" s="70" t="s">
-        <v>12</v>
-      </c>
-      <c r="G17" s="70" t="s">
-        <v>12</v>
-      </c>
-      <c r="H17" s="70" t="s">
-        <v>12</v>
-      </c>
-      <c r="I17" s="70" t="s">
-        <v>12</v>
-      </c>
-      <c r="J17" s="82" t="s">
-        <v>12</v>
+      <c r="A17" s="69" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" s="69" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="69" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" s="69" t="s">
+        <v>9</v>
+      </c>
+      <c r="E17" s="69" t="s">
+        <v>9</v>
+      </c>
+      <c r="F17" s="69" t="s">
+        <v>9</v>
+      </c>
+      <c r="G17" s="69" t="s">
+        <v>9</v>
+      </c>
+      <c r="H17" s="69" t="s">
+        <v>9</v>
+      </c>
+      <c r="I17" s="69" t="s">
+        <v>9</v>
+      </c>
+      <c r="J17" s="81" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="15">
       <c r="A18" s="25" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B18" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="C18" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="D18" s="26" t="s">
+        <v>70</v>
+      </c>
+      <c r="E18" s="26" t="s">
+        <v>71</v>
+      </c>
+      <c r="F18" s="26" t="s">
+        <v>118</v>
+      </c>
+      <c r="G18" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="H18" s="26" t="s">
+        <v>115</v>
+      </c>
+      <c r="I18" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="C18" s="26" t="s">
-        <v>81</v>
-      </c>
-      <c r="D18" s="26" t="s">
-        <v>82</v>
-      </c>
-      <c r="E18" s="26" t="s">
-        <v>83</v>
-      </c>
-      <c r="F18" s="26" t="s">
-        <v>127</v>
-      </c>
-      <c r="G18" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="H18" s="26" t="s">
-        <v>124</v>
-      </c>
-      <c r="I18" s="26" t="s">
-        <v>48</v>
-      </c>
       <c r="J18" s="2" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
     </row>
     <row r="19" spans="1:10">

--- a/data/재난현장지도_표준화_데이터.xlsx
+++ b/data/재난현장지도_표준화_데이터.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\kdr\2.TextDocument\구호사업팀(재해구호관리팀)\--- 2026 구호사업팀\1. 이사랑_2026년 업무\6. 대처현황 상황보고\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\kdr\2.TextDocument\구호사업팀(재해구호관리팀)\--- 2026 구호사업팀\1. 이사랑_2026년 업무\6. 대처현황 상황보고\[8.17.~] 호우 대처현황 상황보고\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>

--- a/data/재난현장지도_표준화_데이터.xlsx
+++ b/data/재난현장지도_표준화_데이터.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\kdr\2.TextDocument\구호사업팀(재해구호관리팀)\--- 2026 구호사업팀\1. 이사랑_2026년 업무\6. 대처현황 상황보고\[8.17.~] 호우 대처현황 상황보고\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -541,11 +541,11 @@
     <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
+    <t>kg</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
     <t>식품·간식</t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
-    <t>kg</t>
     <phoneticPr fontId="13" type="noConversion"/>
   </si>
 </sst>
@@ -1972,7 +1972,7 @@
         <v>63</v>
       </c>
       <c r="E13" s="66" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F13" s="66" t="s">
         <v>126</v>
@@ -2040,7 +2040,7 @@
         <v>96</v>
       </c>
       <c r="H15" s="32" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="I15" s="33"/>
     </row>

--- a/data/재난현장지도_표준화_데이터.xlsx
+++ b/data/재난현장지도_표준화_데이터.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\User\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\kdr\2.TextDocument\구호사업팀(재해구호관리팀)\--- 2026 구호사업팀\1. 이사랑_2026년 업무\6. 대처현황 상황보고\[8.17.~] 호우 대처현황 상황보고\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="15990" windowHeight="8280" firstSheet="1" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15990" windowHeight="8280" firstSheet="1" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="00_사용안내" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="547" uniqueCount="132">
   <si>
     <t>재난 및 구호 현장지도 데이터 표준안</t>
   </si>
@@ -541,11 +541,15 @@
     <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
+    <t>식품·간식</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
     <t>kg</t>
     <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
-    <t>식품·간식</t>
+    <t>kg</t>
     <phoneticPr fontId="13" type="noConversion"/>
   </si>
 </sst>
@@ -1972,7 +1976,7 @@
         <v>63</v>
       </c>
       <c r="E13" s="66" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F13" s="66" t="s">
         <v>126</v>
@@ -1991,30 +1995,16 @@
       <c r="A14" s="28" t="s">
         <v>67</v>
       </c>
-      <c r="B14" s="29">
-        <v>336</v>
-      </c>
-      <c r="C14" s="29">
-        <v>400</v>
-      </c>
-      <c r="D14" s="29">
-        <v>35840</v>
-      </c>
-      <c r="E14" s="29">
-        <v>21112</v>
-      </c>
-      <c r="F14" s="29">
-        <v>2344</v>
-      </c>
-      <c r="G14" s="29">
-        <v>625</v>
-      </c>
-      <c r="H14" s="29">
-        <v>11600</v>
-      </c>
+      <c r="B14" s="29"/>
+      <c r="C14" s="29"/>
+      <c r="D14" s="29"/>
+      <c r="E14" s="29"/>
+      <c r="F14" s="29"/>
+      <c r="G14" s="29"/>
+      <c r="H14" s="29"/>
       <c r="I14" s="30">
         <f>SUM(B14:H14)</f>
-        <v>72257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -2040,7 +2030,7 @@
         <v>96</v>
       </c>
       <c r="H15" s="32" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I15" s="33"/>
     </row>
@@ -2856,24 +2846,26 @@
         <v>336</v>
       </c>
       <c r="C14" s="29">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="D14" s="29">
-        <v>13440</v>
+        <v>35840</v>
       </c>
       <c r="E14" s="29">
-        <v>10742</v>
+        <v>28112</v>
       </c>
       <c r="F14" s="29">
-        <v>1200</v>
+        <v>2344</v>
       </c>
       <c r="G14" s="29">
         <v>625</v>
       </c>
-      <c r="H14" s="29"/>
+      <c r="H14" s="29">
+        <v>16840</v>
+      </c>
       <c r="I14" s="30">
         <f>SUM(B14:H14)</f>
-        <v>26443</v>
+        <v>84497</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -2898,7 +2890,9 @@
       <c r="G15" s="32" t="s">
         <v>96</v>
       </c>
-      <c r="H15" s="32"/>
+      <c r="H15" s="32" t="s">
+        <v>131</v>
+      </c>
       <c r="I15" s="33"/>
     </row>
     <row r="16" spans="1:9">

--- a/data/재난현장지도_표준화_데이터.xlsx
+++ b/data/재난현장지도_표준화_데이터.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="547" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="135">
   <si>
     <t>재난 및 구호 현장지도 데이터 표준안</t>
   </si>
@@ -552,6 +552,18 @@
     <t>kg</t>
     <phoneticPr fontId="13" type="noConversion"/>
   </si>
+  <si>
+    <t>식품·간식</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>기타</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>개</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -562,7 +574,7 @@
     <numFmt numFmtId="177" formatCode="0.0"/>
     <numFmt numFmtId="178" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="18">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -657,6 +669,12 @@
       <b/>
       <sz val="10"/>
       <color rgb="FF111827"/>
+      <name val="돋움"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <name val="돋움"/>
       <family val="3"/>
       <charset val="129"/>
@@ -942,7 +960,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1174,6 +1192,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2598,18 +2619,18 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I40"/>
+  <dimension ref="A1:J40"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="5" width="14" customWidth="1"/>
-    <col min="6" max="7" width="15" customWidth="1"/>
-    <col min="8" max="11" width="18" customWidth="1"/>
+    <col min="6" max="8" width="15" customWidth="1"/>
+    <col min="9" max="12" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="27.95" customHeight="1">
+    <row r="1" spans="1:10" ht="27.95" customHeight="1">
       <c r="A1" s="68" t="s">
         <v>92</v>
       </c>
@@ -2631,14 +2652,15 @@
       <c r="G1" s="68" t="s">
         <v>92</v>
       </c>
-      <c r="H1" s="68" t="s">
-        <v>92</v>
-      </c>
+      <c r="H1" s="68"/>
       <c r="I1" s="68" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="2" spans="1:9">
+      <c r="J1" s="68" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
       <c r="A2" s="17"/>
       <c r="B2" s="17"/>
       <c r="C2" s="17"/>
@@ -2648,8 +2670,9 @@
       <c r="G2" s="17"/>
       <c r="H2" s="17"/>
       <c r="I2" s="17"/>
-    </row>
-    <row r="3" spans="1:9">
+      <c r="J2" s="17"/>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3" s="18" t="s">
         <v>16</v>
       </c>
@@ -2663,8 +2686,9 @@
       <c r="G3" s="17"/>
       <c r="H3" s="17"/>
       <c r="I3" s="17"/>
-    </row>
-    <row r="4" spans="1:9">
+      <c r="J3" s="17"/>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4" s="20" t="s">
         <v>18</v>
       </c>
@@ -2678,8 +2702,9 @@
       <c r="G4" s="17"/>
       <c r="H4" s="17"/>
       <c r="I4" s="17"/>
-    </row>
-    <row r="5" spans="1:9">
+      <c r="J4" s="17"/>
+    </row>
+    <row r="5" spans="1:10">
       <c r="A5" s="20" t="s">
         <v>59</v>
       </c>
@@ -2693,8 +2718,9 @@
       <c r="G5" s="17"/>
       <c r="H5" s="17"/>
       <c r="I5" s="17"/>
-    </row>
-    <row r="6" spans="1:9">
+      <c r="J5" s="17"/>
+    </row>
+    <row r="6" spans="1:10">
       <c r="A6" s="20" t="s">
         <v>60</v>
       </c>
@@ -2708,8 +2734,9 @@
       <c r="G6" s="17"/>
       <c r="H6" s="17"/>
       <c r="I6" s="17"/>
-    </row>
-    <row r="7" spans="1:9">
+      <c r="J6" s="17"/>
+    </row>
+    <row r="7" spans="1:10">
       <c r="A7" s="20" t="s">
         <v>61</v>
       </c>
@@ -2723,8 +2750,9 @@
       <c r="G7" s="17"/>
       <c r="H7" s="17"/>
       <c r="I7" s="17"/>
-    </row>
-    <row r="8" spans="1:9">
+      <c r="J7" s="17"/>
+    </row>
+    <row r="8" spans="1:10">
       <c r="A8" s="20" t="s">
         <v>19</v>
       </c>
@@ -2738,8 +2766,9 @@
       <c r="G8" s="17"/>
       <c r="H8" s="17"/>
       <c r="I8" s="17"/>
-    </row>
-    <row r="9" spans="1:9">
+      <c r="J8" s="17"/>
+    </row>
+    <row r="9" spans="1:10">
       <c r="A9" s="20" t="s">
         <v>20</v>
       </c>
@@ -2753,8 +2782,9 @@
       <c r="G9" s="17"/>
       <c r="H9" s="17"/>
       <c r="I9" s="17"/>
-    </row>
-    <row r="10" spans="1:9">
+      <c r="J9" s="17"/>
+    </row>
+    <row r="10" spans="1:10">
       <c r="A10" s="23" t="s">
         <v>62</v>
       </c>
@@ -2768,8 +2798,9 @@
       <c r="G10" s="17"/>
       <c r="H10" s="17"/>
       <c r="I10" s="17"/>
-    </row>
-    <row r="11" spans="1:9">
+      <c r="J10" s="17"/>
+    </row>
+    <row r="11" spans="1:10">
       <c r="A11" s="17"/>
       <c r="B11" s="17"/>
       <c r="C11" s="17"/>
@@ -2779,8 +2810,9 @@
       <c r="G11" s="17"/>
       <c r="H11" s="17"/>
       <c r="I11" s="17"/>
-    </row>
-    <row r="12" spans="1:9" ht="21.95" customHeight="1">
+      <c r="J11" s="17"/>
+    </row>
+    <row r="12" spans="1:10" ht="21.95" customHeight="1">
       <c r="A12" s="68" t="s">
         <v>7</v>
       </c>
@@ -2802,14 +2834,15 @@
       <c r="G12" s="68" t="s">
         <v>7</v>
       </c>
-      <c r="H12" s="68" t="s">
-        <v>7</v>
-      </c>
+      <c r="H12" s="68"/>
       <c r="I12" s="68" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="13" spans="1:9">
+      <c r="J12" s="68" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
       <c r="A13" s="25" t="s">
         <v>1</v>
       </c>
@@ -2822,8 +2855,8 @@
       <c r="D13" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="E13" s="26" t="s">
-        <v>64</v>
+      <c r="E13" s="66" t="s">
+        <v>132</v>
       </c>
       <c r="F13" s="66" t="s">
         <v>126</v>
@@ -2832,13 +2865,16 @@
         <v>125</v>
       </c>
       <c r="H13" s="66" t="s">
+        <v>133</v>
+      </c>
+      <c r="I13" s="66" t="s">
         <v>124</v>
       </c>
-      <c r="I13" s="27" t="s">
+      <c r="J13" s="27" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="14" spans="1:9">
+    <row r="14" spans="1:10">
       <c r="A14" s="28" t="s">
         <v>67</v>
       </c>
@@ -2861,14 +2897,17 @@
         <v>625</v>
       </c>
       <c r="H14" s="29">
+        <v>2000</v>
+      </c>
+      <c r="I14" s="29">
         <v>16840</v>
       </c>
-      <c r="I14" s="30">
-        <f>SUM(B14:H14)</f>
-        <v>84497</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9">
+      <c r="J14" s="30">
+        <f>SUM(B14:I14)</f>
+        <v>86497</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
       <c r="A15" s="31" t="s">
         <v>21</v>
       </c>
@@ -2890,12 +2929,15 @@
       <c r="G15" s="32" t="s">
         <v>96</v>
       </c>
-      <c r="H15" s="32" t="s">
+      <c r="H15" s="82" t="s">
+        <v>134</v>
+      </c>
+      <c r="I15" s="32" t="s">
         <v>131</v>
       </c>
-      <c r="I15" s="33"/>
-    </row>
-    <row r="16" spans="1:9">
+      <c r="J15" s="33"/>
+    </row>
+    <row r="16" spans="1:10">
       <c r="A16" s="17"/>
       <c r="B16" s="17"/>
       <c r="C16" s="17"/>
@@ -2905,8 +2947,9 @@
       <c r="G16" s="17"/>
       <c r="H16" s="17"/>
       <c r="I16" s="17"/>
-    </row>
-    <row r="17" spans="1:9" ht="21.95" customHeight="1">
+      <c r="J16" s="17"/>
+    </row>
+    <row r="17" spans="1:10" ht="21.95" customHeight="1">
       <c r="A17" s="69" t="s">
         <v>9</v>
       </c>
@@ -2928,14 +2971,15 @@
       <c r="G17" s="69" t="s">
         <v>9</v>
       </c>
-      <c r="H17" s="69" t="s">
-        <v>9</v>
-      </c>
+      <c r="H17" s="69"/>
       <c r="I17" s="69" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="18" spans="1:9">
+      <c r="J17" s="69" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
       <c r="A18" s="25" t="s">
         <v>27</v>
       </c>
@@ -2957,14 +3001,15 @@
       <c r="G18" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="H18" s="26" t="s">
+      <c r="H18" s="26"/>
+      <c r="I18" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="I18" s="27" t="s">
+      <c r="J18" s="27" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="19" spans="1:9">
+    <row r="19" spans="1:10">
       <c r="A19" s="36" t="s">
         <v>89</v>
       </c>
@@ -2980,12 +3025,13 @@
       <c r="G19" s="38">
         <v>1</v>
       </c>
-      <c r="H19" s="38">
+      <c r="H19" s="38"/>
+      <c r="I19" s="38">
         <v>2</v>
       </c>
-      <c r="I19" s="53"/>
-    </row>
-    <row r="20" spans="1:9">
+      <c r="J19" s="53"/>
+    </row>
+    <row r="20" spans="1:10">
       <c r="A20" s="41" t="s">
         <v>89</v>
       </c>
@@ -2999,12 +3045,13 @@
         <v>778.7</v>
       </c>
       <c r="G20" s="43"/>
-      <c r="H20" s="43">
+      <c r="H20" s="43"/>
+      <c r="I20" s="43">
         <v>1</v>
       </c>
-      <c r="I20" s="55"/>
-    </row>
-    <row r="21" spans="1:9">
+      <c r="J20" s="55"/>
+    </row>
+    <row r="21" spans="1:10">
       <c r="A21" s="41" t="s">
         <v>77</v>
       </c>
@@ -3019,11 +3066,12 @@
       </c>
       <c r="G21" s="43"/>
       <c r="H21" s="43"/>
-      <c r="I21" s="55" t="s">
+      <c r="I21" s="43"/>
+      <c r="J21" s="55" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="22" spans="1:9">
+    <row r="22" spans="1:10">
       <c r="A22" s="41" t="s">
         <v>90</v>
       </c>
@@ -3038,11 +3086,12 @@
       </c>
       <c r="G22" s="43"/>
       <c r="H22" s="43"/>
-      <c r="I22" s="55" t="s">
+      <c r="I22" s="43"/>
+      <c r="J22" s="55" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="23" spans="1:9">
+    <row r="23" spans="1:10">
       <c r="A23" s="41" t="s">
         <v>89</v>
       </c>
@@ -3057,9 +3106,10 @@
       </c>
       <c r="G23" s="43"/>
       <c r="H23" s="43"/>
-      <c r="I23" s="55"/>
-    </row>
-    <row r="24" spans="1:9">
+      <c r="I23" s="43"/>
+      <c r="J23" s="55"/>
+    </row>
+    <row r="24" spans="1:10">
       <c r="A24" s="41" t="s">
         <v>89</v>
       </c>
@@ -3074,9 +3124,10 @@
       </c>
       <c r="G24" s="43"/>
       <c r="H24" s="43"/>
-      <c r="I24" s="55"/>
-    </row>
-    <row r="25" spans="1:9">
+      <c r="I24" s="43"/>
+      <c r="J24" s="55"/>
+    </row>
+    <row r="25" spans="1:10">
       <c r="A25" s="46" t="s">
         <v>81</v>
       </c>
@@ -3086,14 +3137,15 @@
       <c r="E25" s="47"/>
       <c r="F25" s="56"/>
       <c r="G25" s="48"/>
-      <c r="H25" s="48">
+      <c r="H25" s="48"/>
+      <c r="I25" s="48">
         <v>1</v>
       </c>
-      <c r="I25" s="57" t="s">
+      <c r="J25" s="57" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="26" spans="1:9">
+    <row r="26" spans="1:10">
       <c r="A26" s="17"/>
       <c r="B26" s="17"/>
       <c r="C26" s="17"/>
@@ -3103,8 +3155,9 @@
       <c r="G26" s="17"/>
       <c r="H26" s="17"/>
       <c r="I26" s="17"/>
-    </row>
-    <row r="27" spans="1:9">
+      <c r="J26" s="17"/>
+    </row>
+    <row r="27" spans="1:10">
       <c r="A27" s="17"/>
       <c r="B27" s="17"/>
       <c r="C27" s="17"/>
@@ -3114,8 +3167,9 @@
       <c r="G27" s="17"/>
       <c r="H27" s="17"/>
       <c r="I27" s="17"/>
-    </row>
-    <row r="28" spans="1:9">
+      <c r="J27" s="17"/>
+    </row>
+    <row r="28" spans="1:10">
       <c r="A28" s="17"/>
       <c r="B28" s="17"/>
       <c r="C28" s="17"/>
@@ -3125,8 +3179,9 @@
       <c r="G28" s="17"/>
       <c r="H28" s="17"/>
       <c r="I28" s="17"/>
-    </row>
-    <row r="29" spans="1:9">
+      <c r="J28" s="17"/>
+    </row>
+    <row r="29" spans="1:10">
       <c r="A29" s="17"/>
       <c r="B29" s="17"/>
       <c r="C29" s="17"/>
@@ -3136,8 +3191,9 @@
       <c r="G29" s="17"/>
       <c r="H29" s="17"/>
       <c r="I29" s="17"/>
-    </row>
-    <row r="30" spans="1:9">
+      <c r="J29" s="17"/>
+    </row>
+    <row r="30" spans="1:10">
       <c r="A30" s="17"/>
       <c r="B30" s="17"/>
       <c r="C30" s="17"/>
@@ -3147,8 +3203,9 @@
       <c r="G30" s="17"/>
       <c r="H30" s="17"/>
       <c r="I30" s="17"/>
-    </row>
-    <row r="31" spans="1:9">
+      <c r="J30" s="17"/>
+    </row>
+    <row r="31" spans="1:10">
       <c r="A31" s="17"/>
       <c r="B31" s="17"/>
       <c r="C31" s="17"/>
@@ -3158,8 +3215,9 @@
       <c r="G31" s="17"/>
       <c r="H31" s="17"/>
       <c r="I31" s="17"/>
-    </row>
-    <row r="32" spans="1:9">
+      <c r="J31" s="17"/>
+    </row>
+    <row r="32" spans="1:10">
       <c r="A32" s="17"/>
       <c r="B32" s="17"/>
       <c r="C32" s="17"/>
@@ -3169,8 +3227,9 @@
       <c r="G32" s="17"/>
       <c r="H32" s="17"/>
       <c r="I32" s="17"/>
-    </row>
-    <row r="33" spans="1:9">
+      <c r="J32" s="17"/>
+    </row>
+    <row r="33" spans="1:10">
       <c r="A33" s="17"/>
       <c r="B33" s="17"/>
       <c r="C33" s="17"/>
@@ -3180,8 +3239,9 @@
       <c r="G33" s="17"/>
       <c r="H33" s="17"/>
       <c r="I33" s="17"/>
-    </row>
-    <row r="34" spans="1:9">
+      <c r="J33" s="17"/>
+    </row>
+    <row r="34" spans="1:10">
       <c r="A34" s="17"/>
       <c r="B34" s="17"/>
       <c r="C34" s="17"/>
@@ -3191,8 +3251,9 @@
       <c r="G34" s="17"/>
       <c r="H34" s="17"/>
       <c r="I34" s="17"/>
-    </row>
-    <row r="35" spans="1:9">
+      <c r="J34" s="17"/>
+    </row>
+    <row r="35" spans="1:10">
       <c r="A35" s="17"/>
       <c r="B35" s="17"/>
       <c r="C35" s="17"/>
@@ -3202,8 +3263,9 @@
       <c r="G35" s="17"/>
       <c r="H35" s="17"/>
       <c r="I35" s="17"/>
-    </row>
-    <row r="36" spans="1:9">
+      <c r="J35" s="17"/>
+    </row>
+    <row r="36" spans="1:10">
       <c r="A36" s="17"/>
       <c r="B36" s="17"/>
       <c r="C36" s="17"/>
@@ -3213,8 +3275,9 @@
       <c r="G36" s="17"/>
       <c r="H36" s="17"/>
       <c r="I36" s="17"/>
-    </row>
-    <row r="37" spans="1:9">
+      <c r="J36" s="17"/>
+    </row>
+    <row r="37" spans="1:10">
       <c r="A37" s="17"/>
       <c r="B37" s="17"/>
       <c r="C37" s="17"/>
@@ -3224,8 +3287,9 @@
       <c r="G37" s="17"/>
       <c r="H37" s="17"/>
       <c r="I37" s="17"/>
-    </row>
-    <row r="38" spans="1:9">
+      <c r="J37" s="17"/>
+    </row>
+    <row r="38" spans="1:10">
       <c r="A38" s="17"/>
       <c r="B38" s="17"/>
       <c r="C38" s="17"/>
@@ -3235,8 +3299,9 @@
       <c r="G38" s="17"/>
       <c r="H38" s="17"/>
       <c r="I38" s="17"/>
-    </row>
-    <row r="39" spans="1:9">
+      <c r="J38" s="17"/>
+    </row>
+    <row r="39" spans="1:10">
       <c r="A39" s="17"/>
       <c r="B39" s="17"/>
       <c r="C39" s="17"/>
@@ -3246,8 +3311,9 @@
       <c r="G39" s="17"/>
       <c r="H39" s="17"/>
       <c r="I39" s="17"/>
-    </row>
-    <row r="40" spans="1:9">
+      <c r="J39" s="17"/>
+    </row>
+    <row r="40" spans="1:10">
       <c r="A40" s="17"/>
       <c r="B40" s="17"/>
       <c r="C40" s="17"/>
@@ -3257,12 +3323,13 @@
       <c r="G40" s="17"/>
       <c r="H40" s="17"/>
       <c r="I40" s="17"/>
+      <c r="J40" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A12:I12"/>
-    <mergeCell ref="A17:I17"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A12:J12"/>
+    <mergeCell ref="A17:J17"/>
   </mergeCells>
   <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/재난현장지도_표준화_데이터.xlsx
+++ b/data/재난현장지도_표준화_데이터.xlsx
@@ -1148,6 +1148,9 @@
     <xf numFmtId="0" fontId="16" fillId="3" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1192,9 +1195,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1418,28 +1418,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="27.95" customHeight="1">
-      <c r="A1" s="67" t="s">
+      <c r="A1" s="68" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="67" t="s">
+      <c r="B1" s="68" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="67" t="s">
+      <c r="C1" s="68" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="67" t="s">
+      <c r="D1" s="68" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="67" t="s">
+      <c r="E1" s="68" t="s">
         <v>0</v>
       </c>
-      <c r="F1" s="67" t="s">
+      <c r="F1" s="68" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="67" t="s">
+      <c r="G1" s="68" t="s">
         <v>0</v>
       </c>
-      <c r="H1" s="67" t="s">
+      <c r="H1" s="68" t="s">
         <v>0</v>
       </c>
     </row>
@@ -1529,31 +1529,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="27.95" customHeight="1">
-      <c r="A1" s="67" t="s">
+      <c r="A1" s="68" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="67" t="s">
+      <c r="B1" s="68" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="67" t="s">
+      <c r="C1" s="68" t="s">
         <v>15</v>
       </c>
-      <c r="D1" s="67" t="s">
+      <c r="D1" s="68" t="s">
         <v>15</v>
       </c>
-      <c r="E1" s="67" t="s">
+      <c r="E1" s="68" t="s">
         <v>15</v>
       </c>
-      <c r="F1" s="67" t="s">
+      <c r="F1" s="68" t="s">
         <v>15</v>
       </c>
-      <c r="G1" s="67" t="s">
+      <c r="G1" s="68" t="s">
         <v>15</v>
       </c>
-      <c r="H1" s="67" t="s">
+      <c r="H1" s="68" t="s">
         <v>15</v>
       </c>
-      <c r="I1" s="67" t="s">
+      <c r="I1" s="68" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1786,31 +1786,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="27.95" customHeight="1">
-      <c r="A1" s="68" t="s">
+      <c r="A1" s="69" t="s">
         <v>58</v>
       </c>
-      <c r="B1" s="68" t="s">
+      <c r="B1" s="69" t="s">
         <v>58</v>
       </c>
-      <c r="C1" s="68" t="s">
+      <c r="C1" s="69" t="s">
         <v>58</v>
       </c>
-      <c r="D1" s="68" t="s">
+      <c r="D1" s="69" t="s">
         <v>58</v>
       </c>
-      <c r="E1" s="68" t="s">
+      <c r="E1" s="69" t="s">
         <v>58</v>
       </c>
-      <c r="F1" s="68" t="s">
+      <c r="F1" s="69" t="s">
         <v>58</v>
       </c>
-      <c r="G1" s="68" t="s">
+      <c r="G1" s="69" t="s">
         <v>58</v>
       </c>
-      <c r="H1" s="68" t="s">
+      <c r="H1" s="69" t="s">
         <v>58</v>
       </c>
-      <c r="I1" s="68" t="s">
+      <c r="I1" s="69" t="s">
         <v>58</v>
       </c>
     </row>
@@ -1955,31 +1955,31 @@
       <c r="I11" s="17"/>
     </row>
     <row r="12" spans="1:9" ht="21.95" customHeight="1">
-      <c r="A12" s="68" t="s">
+      <c r="A12" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="B12" s="68" t="s">
+      <c r="B12" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="68" t="s">
+      <c r="C12" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="68" t="s">
+      <c r="D12" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="E12" s="68" t="s">
+      <c r="E12" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="F12" s="68" t="s">
+      <c r="F12" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="G12" s="68" t="s">
+      <c r="G12" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="H12" s="68" t="s">
+      <c r="H12" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="I12" s="68" t="s">
+      <c r="I12" s="69" t="s">
         <v>7</v>
       </c>
     </row>
@@ -2067,31 +2067,31 @@
       <c r="I16" s="17"/>
     </row>
     <row r="17" spans="1:11" ht="21.95" customHeight="1">
-      <c r="A17" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="B17" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="C17" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="D17" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="E17" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="F17" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="G17" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="H17" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="I17" s="69" t="s">
+      <c r="A17" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="E17" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="F17" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="G17" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="H17" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="I17" s="70" t="s">
         <v>9</v>
       </c>
       <c r="J17" s="35"/>
@@ -2566,32 +2566,32 @@
       <c r="I37" s="17"/>
     </row>
     <row r="38" spans="1:11">
-      <c r="A38" s="70" t="s">
+      <c r="A38" s="71" t="s">
         <v>91</v>
       </c>
-      <c r="B38" s="70"/>
-      <c r="C38" s="70"/>
-      <c r="D38" s="70"/>
-      <c r="E38" s="70"/>
-      <c r="F38" s="70"/>
-      <c r="G38" s="70"/>
-      <c r="H38" s="70"/>
-      <c r="I38" s="70"/>
-      <c r="J38" s="71"/>
-      <c r="K38" s="71"/>
+      <c r="B38" s="71"/>
+      <c r="C38" s="71"/>
+      <c r="D38" s="71"/>
+      <c r="E38" s="71"/>
+      <c r="F38" s="71"/>
+      <c r="G38" s="71"/>
+      <c r="H38" s="71"/>
+      <c r="I38" s="71"/>
+      <c r="J38" s="72"/>
+      <c r="K38" s="72"/>
     </row>
     <row r="39" spans="1:11">
-      <c r="A39" s="70"/>
-      <c r="B39" s="70"/>
-      <c r="C39" s="70"/>
-      <c r="D39" s="70"/>
-      <c r="E39" s="70"/>
-      <c r="F39" s="70"/>
-      <c r="G39" s="70"/>
-      <c r="H39" s="70"/>
-      <c r="I39" s="70"/>
-      <c r="J39" s="71"/>
-      <c r="K39" s="71"/>
+      <c r="A39" s="71"/>
+      <c r="B39" s="71"/>
+      <c r="C39" s="71"/>
+      <c r="D39" s="71"/>
+      <c r="E39" s="71"/>
+      <c r="F39" s="71"/>
+      <c r="G39" s="71"/>
+      <c r="H39" s="71"/>
+      <c r="I39" s="71"/>
+      <c r="J39" s="72"/>
+      <c r="K39" s="72"/>
     </row>
     <row r="40" spans="1:11">
       <c r="A40" s="17"/>
@@ -2631,32 +2631,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="27.95" customHeight="1">
-      <c r="A1" s="68" t="s">
+      <c r="A1" s="69" t="s">
         <v>92</v>
       </c>
-      <c r="B1" s="68" t="s">
+      <c r="B1" s="69" t="s">
         <v>92</v>
       </c>
-      <c r="C1" s="68" t="s">
+      <c r="C1" s="69" t="s">
         <v>92</v>
       </c>
-      <c r="D1" s="68" t="s">
+      <c r="D1" s="69" t="s">
         <v>92</v>
       </c>
-      <c r="E1" s="68" t="s">
+      <c r="E1" s="69" t="s">
         <v>92</v>
       </c>
-      <c r="F1" s="68" t="s">
+      <c r="F1" s="69" t="s">
         <v>92</v>
       </c>
-      <c r="G1" s="68" t="s">
+      <c r="G1" s="69" t="s">
         <v>92</v>
       </c>
-      <c r="H1" s="68"/>
-      <c r="I1" s="68" t="s">
+      <c r="H1" s="69"/>
+      <c r="I1" s="69" t="s">
         <v>92</v>
       </c>
-      <c r="J1" s="68" t="s">
+      <c r="J1" s="69" t="s">
         <v>92</v>
       </c>
     </row>
@@ -2813,32 +2813,32 @@
       <c r="J11" s="17"/>
     </row>
     <row r="12" spans="1:10" ht="21.95" customHeight="1">
-      <c r="A12" s="68" t="s">
+      <c r="A12" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="B12" s="68" t="s">
+      <c r="B12" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="68" t="s">
+      <c r="C12" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="68" t="s">
+      <c r="D12" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="E12" s="68" t="s">
+      <c r="E12" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="F12" s="68" t="s">
+      <c r="F12" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="G12" s="68" t="s">
+      <c r="G12" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="H12" s="68"/>
-      <c r="I12" s="68" t="s">
+      <c r="H12" s="69"/>
+      <c r="I12" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="J12" s="68" t="s">
+      <c r="J12" s="69" t="s">
         <v>7</v>
       </c>
     </row>
@@ -2900,11 +2900,11 @@
         <v>2000</v>
       </c>
       <c r="I14" s="29">
-        <v>16840</v>
+        <v>17780</v>
       </c>
       <c r="J14" s="30">
         <f>SUM(B14:I14)</f>
-        <v>86497</v>
+        <v>87437</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -2929,7 +2929,7 @@
       <c r="G15" s="32" t="s">
         <v>96</v>
       </c>
-      <c r="H15" s="82" t="s">
+      <c r="H15" s="67" t="s">
         <v>134</v>
       </c>
       <c r="I15" s="32" t="s">
@@ -2950,32 +2950,32 @@
       <c r="J16" s="17"/>
     </row>
     <row r="17" spans="1:10" ht="21.95" customHeight="1">
-      <c r="A17" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="B17" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="C17" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="D17" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="E17" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="F17" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="G17" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="H17" s="69"/>
-      <c r="I17" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="J17" s="69" t="s">
+      <c r="A17" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="E17" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="F17" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="G17" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="H17" s="70"/>
+      <c r="I17" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="J17" s="70" t="s">
         <v>9</v>
       </c>
     </row>
@@ -3350,34 +3350,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="27.95" customHeight="1">
-      <c r="A1" s="68" t="s">
+      <c r="A1" s="69" t="s">
         <v>106</v>
       </c>
-      <c r="B1" s="68" t="s">
+      <c r="B1" s="69" t="s">
         <v>106</v>
       </c>
-      <c r="C1" s="68" t="s">
+      <c r="C1" s="69" t="s">
         <v>106</v>
       </c>
-      <c r="D1" s="68" t="s">
+      <c r="D1" s="69" t="s">
         <v>106</v>
       </c>
-      <c r="E1" s="68" t="s">
+      <c r="E1" s="69" t="s">
         <v>106</v>
       </c>
-      <c r="F1" s="68" t="s">
+      <c r="F1" s="69" t="s">
         <v>106</v>
       </c>
-      <c r="G1" s="68" t="s">
+      <c r="G1" s="69" t="s">
         <v>106</v>
       </c>
-      <c r="H1" s="68" t="s">
+      <c r="H1" s="69" t="s">
         <v>106</v>
       </c>
-      <c r="I1" s="68" t="s">
+      <c r="I1" s="69" t="s">
         <v>106</v>
       </c>
-      <c r="J1" s="67" t="s">
+      <c r="J1" s="68" t="s">
         <v>106</v>
       </c>
     </row>
@@ -3400,14 +3400,14 @@
         <v>39</v>
       </c>
       <c r="C3" s="17"/>
-      <c r="D3" s="72" t="s">
+      <c r="D3" s="73" t="s">
         <v>107</v>
       </c>
-      <c r="E3" s="73"/>
-      <c r="F3" s="73"/>
-      <c r="G3" s="73"/>
-      <c r="H3" s="73"/>
-      <c r="I3" s="74"/>
+      <c r="E3" s="74"/>
+      <c r="F3" s="74"/>
+      <c r="G3" s="74"/>
+      <c r="H3" s="74"/>
+      <c r="I3" s="75"/>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="20" t="s">
@@ -3417,12 +3417,12 @@
         <v>40</v>
       </c>
       <c r="C4" s="17"/>
-      <c r="D4" s="75"/>
-      <c r="E4" s="76"/>
-      <c r="F4" s="76"/>
-      <c r="G4" s="76"/>
-      <c r="H4" s="76"/>
-      <c r="I4" s="77"/>
+      <c r="D4" s="76"/>
+      <c r="E4" s="77"/>
+      <c r="F4" s="77"/>
+      <c r="G4" s="77"/>
+      <c r="H4" s="77"/>
+      <c r="I4" s="78"/>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="20" t="s">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="B5" s="22"/>
       <c r="C5" s="17"/>
-      <c r="D5" s="78"/>
-      <c r="E5" s="79"/>
-      <c r="F5" s="79"/>
-      <c r="G5" s="79"/>
-      <c r="H5" s="79"/>
-      <c r="I5" s="80"/>
+      <c r="D5" s="79"/>
+      <c r="E5" s="80"/>
+      <c r="F5" s="80"/>
+      <c r="G5" s="80"/>
+      <c r="H5" s="80"/>
+      <c r="I5" s="81"/>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="20" t="s">
@@ -3520,31 +3520,31 @@
       <c r="I11" s="17"/>
     </row>
     <row r="12" spans="1:10" ht="21.95" customHeight="1">
-      <c r="A12" s="68" t="s">
+      <c r="A12" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="B12" s="68" t="s">
+      <c r="B12" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="68" t="s">
+      <c r="C12" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="68" t="s">
+      <c r="D12" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="E12" s="68" t="s">
+      <c r="E12" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="F12" s="68" t="s">
+      <c r="F12" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="G12" s="68" t="s">
+      <c r="G12" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="H12" s="68" t="s">
+      <c r="H12" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="I12" s="68" t="s">
+      <c r="I12" s="69" t="s">
         <v>7</v>
       </c>
     </row>
@@ -3627,34 +3627,34 @@
       <c r="I16" s="17"/>
     </row>
     <row r="17" spans="1:10" ht="21.95" customHeight="1">
-      <c r="A17" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="B17" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="C17" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="D17" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="E17" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="F17" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="G17" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="H17" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="I17" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="J17" s="81" t="s">
+      <c r="A17" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="E17" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="F17" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="G17" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="H17" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="I17" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="J17" s="82" t="s">
         <v>9</v>
       </c>
     </row>
@@ -3963,34 +3963,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="27.95" customHeight="1">
-      <c r="A1" s="68" t="s">
+      <c r="A1" s="69" t="s">
         <v>111</v>
       </c>
-      <c r="B1" s="68" t="s">
+      <c r="B1" s="69" t="s">
         <v>111</v>
       </c>
-      <c r="C1" s="68" t="s">
+      <c r="C1" s="69" t="s">
         <v>111</v>
       </c>
-      <c r="D1" s="68" t="s">
+      <c r="D1" s="69" t="s">
         <v>111</v>
       </c>
-      <c r="E1" s="68" t="s">
+      <c r="E1" s="69" t="s">
         <v>111</v>
       </c>
-      <c r="F1" s="68" t="s">
+      <c r="F1" s="69" t="s">
         <v>111</v>
       </c>
-      <c r="G1" s="68" t="s">
+      <c r="G1" s="69" t="s">
         <v>111</v>
       </c>
-      <c r="H1" s="68" t="s">
+      <c r="H1" s="69" t="s">
         <v>111</v>
       </c>
-      <c r="I1" s="68" t="s">
+      <c r="I1" s="69" t="s">
         <v>111</v>
       </c>
-      <c r="J1" s="67" t="s">
+      <c r="J1" s="68" t="s">
         <v>111</v>
       </c>
     </row>
@@ -4013,14 +4013,14 @@
         <v>46</v>
       </c>
       <c r="C3" s="17"/>
-      <c r="D3" s="72" t="s">
+      <c r="D3" s="73" t="s">
         <v>107</v>
       </c>
-      <c r="E3" s="73"/>
-      <c r="F3" s="73"/>
-      <c r="G3" s="73"/>
-      <c r="H3" s="73"/>
-      <c r="I3" s="74"/>
+      <c r="E3" s="74"/>
+      <c r="F3" s="74"/>
+      <c r="G3" s="74"/>
+      <c r="H3" s="74"/>
+      <c r="I3" s="75"/>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="20" t="s">
@@ -4030,12 +4030,12 @@
         <v>40</v>
       </c>
       <c r="C4" s="17"/>
-      <c r="D4" s="75"/>
-      <c r="E4" s="76"/>
-      <c r="F4" s="76"/>
-      <c r="G4" s="76"/>
-      <c r="H4" s="76"/>
-      <c r="I4" s="77"/>
+      <c r="D4" s="76"/>
+      <c r="E4" s="77"/>
+      <c r="F4" s="77"/>
+      <c r="G4" s="77"/>
+      <c r="H4" s="77"/>
+      <c r="I4" s="78"/>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="20" t="s">
@@ -4043,12 +4043,12 @@
       </c>
       <c r="B5" s="22"/>
       <c r="C5" s="17"/>
-      <c r="D5" s="78"/>
-      <c r="E5" s="79"/>
-      <c r="F5" s="79"/>
-      <c r="G5" s="79"/>
-      <c r="H5" s="79"/>
-      <c r="I5" s="80"/>
+      <c r="D5" s="79"/>
+      <c r="E5" s="80"/>
+      <c r="F5" s="80"/>
+      <c r="G5" s="80"/>
+      <c r="H5" s="80"/>
+      <c r="I5" s="81"/>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="20" t="s">
@@ -4133,31 +4133,31 @@
       <c r="I11" s="17"/>
     </row>
     <row r="12" spans="1:10" ht="21.95" customHeight="1">
-      <c r="A12" s="68" t="s">
+      <c r="A12" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="B12" s="68" t="s">
+      <c r="B12" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="68" t="s">
+      <c r="C12" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="68" t="s">
+      <c r="D12" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="E12" s="68" t="s">
+      <c r="E12" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="F12" s="68" t="s">
+      <c r="F12" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="G12" s="68" t="s">
+      <c r="G12" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="H12" s="68" t="s">
+      <c r="H12" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="I12" s="68" t="s">
+      <c r="I12" s="69" t="s">
         <v>7</v>
       </c>
     </row>
@@ -4240,34 +4240,34 @@
       <c r="I16" s="17"/>
     </row>
     <row r="17" spans="1:10" ht="21.95" customHeight="1">
-      <c r="A17" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="B17" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="C17" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="D17" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="E17" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="F17" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="G17" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="H17" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="I17" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="J17" s="81" t="s">
+      <c r="A17" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="E17" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="F17" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="G17" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="H17" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="I17" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="J17" s="82" t="s">
         <v>9</v>
       </c>
     </row>
@@ -4576,34 +4576,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="27.95" customHeight="1">
-      <c r="A1" s="68" t="s">
+      <c r="A1" s="69" t="s">
         <v>113</v>
       </c>
-      <c r="B1" s="68" t="s">
+      <c r="B1" s="69" t="s">
         <v>113</v>
       </c>
-      <c r="C1" s="68" t="s">
+      <c r="C1" s="69" t="s">
         <v>113</v>
       </c>
-      <c r="D1" s="68" t="s">
+      <c r="D1" s="69" t="s">
         <v>113</v>
       </c>
-      <c r="E1" s="68" t="s">
+      <c r="E1" s="69" t="s">
         <v>113</v>
       </c>
-      <c r="F1" s="68" t="s">
+      <c r="F1" s="69" t="s">
         <v>113</v>
       </c>
-      <c r="G1" s="68" t="s">
+      <c r="G1" s="69" t="s">
         <v>113</v>
       </c>
-      <c r="H1" s="68" t="s">
+      <c r="H1" s="69" t="s">
         <v>113</v>
       </c>
-      <c r="I1" s="68" t="s">
+      <c r="I1" s="69" t="s">
         <v>113</v>
       </c>
-      <c r="J1" s="67" t="s">
+      <c r="J1" s="68" t="s">
         <v>113</v>
       </c>
     </row>
@@ -4626,14 +4626,14 @@
         <v>50</v>
       </c>
       <c r="C3" s="17"/>
-      <c r="D3" s="72" t="s">
+      <c r="D3" s="73" t="s">
         <v>107</v>
       </c>
-      <c r="E3" s="73"/>
-      <c r="F3" s="73"/>
-      <c r="G3" s="73"/>
-      <c r="H3" s="73"/>
-      <c r="I3" s="74"/>
+      <c r="E3" s="74"/>
+      <c r="F3" s="74"/>
+      <c r="G3" s="74"/>
+      <c r="H3" s="74"/>
+      <c r="I3" s="75"/>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="20" t="s">
@@ -4643,12 +4643,12 @@
         <v>40</v>
       </c>
       <c r="C4" s="17"/>
-      <c r="D4" s="75"/>
-      <c r="E4" s="76"/>
-      <c r="F4" s="76"/>
-      <c r="G4" s="76"/>
-      <c r="H4" s="76"/>
-      <c r="I4" s="77"/>
+      <c r="D4" s="76"/>
+      <c r="E4" s="77"/>
+      <c r="F4" s="77"/>
+      <c r="G4" s="77"/>
+      <c r="H4" s="77"/>
+      <c r="I4" s="78"/>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="20" t="s">
@@ -4656,12 +4656,12 @@
       </c>
       <c r="B5" s="22"/>
       <c r="C5" s="17"/>
-      <c r="D5" s="78"/>
-      <c r="E5" s="79"/>
-      <c r="F5" s="79"/>
-      <c r="G5" s="79"/>
-      <c r="H5" s="79"/>
-      <c r="I5" s="80"/>
+      <c r="D5" s="79"/>
+      <c r="E5" s="80"/>
+      <c r="F5" s="80"/>
+      <c r="G5" s="80"/>
+      <c r="H5" s="80"/>
+      <c r="I5" s="81"/>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="20" t="s">
@@ -4746,31 +4746,31 @@
       <c r="I11" s="17"/>
     </row>
     <row r="12" spans="1:10" ht="21.95" customHeight="1">
-      <c r="A12" s="68" t="s">
+      <c r="A12" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="B12" s="68" t="s">
+      <c r="B12" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="68" t="s">
+      <c r="C12" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="68" t="s">
+      <c r="D12" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="E12" s="68" t="s">
+      <c r="E12" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="F12" s="68" t="s">
+      <c r="F12" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="G12" s="68" t="s">
+      <c r="G12" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="H12" s="68" t="s">
+      <c r="H12" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="I12" s="68" t="s">
+      <c r="I12" s="69" t="s">
         <v>7</v>
       </c>
     </row>
@@ -4853,34 +4853,34 @@
       <c r="I16" s="17"/>
     </row>
     <row r="17" spans="1:10" ht="21.95" customHeight="1">
-      <c r="A17" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="B17" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="C17" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="D17" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="E17" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="F17" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="G17" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="H17" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="I17" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="J17" s="81" t="s">
+      <c r="A17" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="E17" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="F17" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="G17" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="H17" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="I17" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="J17" s="82" t="s">
         <v>9</v>
       </c>
     </row>
@@ -5189,34 +5189,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="27.95" customHeight="1">
-      <c r="A1" s="68" t="s">
+      <c r="A1" s="69" t="s">
         <v>117</v>
       </c>
-      <c r="B1" s="68" t="s">
+      <c r="B1" s="69" t="s">
         <v>117</v>
       </c>
-      <c r="C1" s="68" t="s">
+      <c r="C1" s="69" t="s">
         <v>117</v>
       </c>
-      <c r="D1" s="68" t="s">
+      <c r="D1" s="69" t="s">
         <v>117</v>
       </c>
-      <c r="E1" s="68" t="s">
+      <c r="E1" s="69" t="s">
         <v>117</v>
       </c>
-      <c r="F1" s="68" t="s">
+      <c r="F1" s="69" t="s">
         <v>117</v>
       </c>
-      <c r="G1" s="68" t="s">
+      <c r="G1" s="69" t="s">
         <v>117</v>
       </c>
-      <c r="H1" s="68" t="s">
+      <c r="H1" s="69" t="s">
         <v>117</v>
       </c>
-      <c r="I1" s="68" t="s">
+      <c r="I1" s="69" t="s">
         <v>117</v>
       </c>
-      <c r="J1" s="67" t="s">
+      <c r="J1" s="68" t="s">
         <v>117</v>
       </c>
     </row>
@@ -5239,14 +5239,14 @@
         <v>55</v>
       </c>
       <c r="C3" s="17"/>
-      <c r="D3" s="72" t="s">
+      <c r="D3" s="73" t="s">
         <v>107</v>
       </c>
-      <c r="E3" s="73"/>
-      <c r="F3" s="73"/>
-      <c r="G3" s="73"/>
-      <c r="H3" s="73"/>
-      <c r="I3" s="74"/>
+      <c r="E3" s="74"/>
+      <c r="F3" s="74"/>
+      <c r="G3" s="74"/>
+      <c r="H3" s="74"/>
+      <c r="I3" s="75"/>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="20" t="s">
@@ -5256,12 +5256,12 @@
         <v>40</v>
       </c>
       <c r="C4" s="17"/>
-      <c r="D4" s="75"/>
-      <c r="E4" s="76"/>
-      <c r="F4" s="76"/>
-      <c r="G4" s="76"/>
-      <c r="H4" s="76"/>
-      <c r="I4" s="77"/>
+      <c r="D4" s="76"/>
+      <c r="E4" s="77"/>
+      <c r="F4" s="77"/>
+      <c r="G4" s="77"/>
+      <c r="H4" s="77"/>
+      <c r="I4" s="78"/>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="20" t="s">
@@ -5269,12 +5269,12 @@
       </c>
       <c r="B5" s="22"/>
       <c r="C5" s="17"/>
-      <c r="D5" s="78"/>
-      <c r="E5" s="79"/>
-      <c r="F5" s="79"/>
-      <c r="G5" s="79"/>
-      <c r="H5" s="79"/>
-      <c r="I5" s="80"/>
+      <c r="D5" s="79"/>
+      <c r="E5" s="80"/>
+      <c r="F5" s="80"/>
+      <c r="G5" s="80"/>
+      <c r="H5" s="80"/>
+      <c r="I5" s="81"/>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="20" t="s">
@@ -5359,31 +5359,31 @@
       <c r="I11" s="17"/>
     </row>
     <row r="12" spans="1:10" ht="21.95" customHeight="1">
-      <c r="A12" s="68" t="s">
+      <c r="A12" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="B12" s="68" t="s">
+      <c r="B12" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="68" t="s">
+      <c r="C12" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="68" t="s">
+      <c r="D12" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="E12" s="68" t="s">
+      <c r="E12" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="F12" s="68" t="s">
+      <c r="F12" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="G12" s="68" t="s">
+      <c r="G12" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="H12" s="68" t="s">
+      <c r="H12" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="I12" s="68" t="s">
+      <c r="I12" s="69" t="s">
         <v>7</v>
       </c>
     </row>
@@ -5466,34 +5466,34 @@
       <c r="I16" s="17"/>
     </row>
     <row r="17" spans="1:10" ht="21.95" customHeight="1">
-      <c r="A17" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="B17" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="C17" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="D17" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="E17" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="F17" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="G17" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="H17" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="I17" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="J17" s="81" t="s">
+      <c r="A17" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="E17" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="F17" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="G17" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="H17" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="I17" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="J17" s="82" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/재난현장지도_표준화_데이터.xlsx
+++ b/data/재난현장지도_표준화_데이터.xlsx
@@ -2888,7 +2888,7 @@
         <v>35840</v>
       </c>
       <c r="E14" s="29">
-        <v>28112</v>
+        <v>36112</v>
       </c>
       <c r="F14" s="29">
         <v>2344</v>
@@ -2897,14 +2897,14 @@
         <v>625</v>
       </c>
       <c r="H14" s="29">
-        <v>2000</v>
+        <v>12000</v>
       </c>
       <c r="I14" s="29">
-        <v>17780</v>
+        <v>18180</v>
       </c>
       <c r="J14" s="30">
         <f>SUM(B14:I14)</f>
-        <v>87437</v>
+        <v>105837</v>
       </c>
     </row>
     <row r="15" spans="1:10">

--- a/data/재난현장지도_표준화_데이터.xlsx
+++ b/data/재난현장지도_표준화_데이터.xlsx
@@ -2879,7 +2879,7 @@
         <v>67</v>
       </c>
       <c r="B14" s="29">
-        <v>336</v>
+        <v>556</v>
       </c>
       <c r="C14" s="29">
         <v>400</v>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="J14" s="30">
         <f>SUM(B14:I14)</f>
-        <v>105837</v>
+        <v>106057</v>
       </c>
     </row>
     <row r="15" spans="1:10">
